--- a/data/raw/Cell_Counts/Stra8_100nMRA/20250104_100nMRA_Stra8_Counts.xlsx
+++ b/data/raw/Cell_Counts/Stra8_100nMRA/20250104_100nMRA_Stra8_Counts.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kbonefas\OneDrive - Michigan Medicine\Desktop\Cell_Counts\Stra8_100nMRA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://umhealth-my.sharepoint.com/personal/kbonefas_med_umich_edu/Documents/Documents/KDM5C_Germ_Mechanism/data/raw/Cell_Counts/Stra8_100nMRA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB1CBD6F-272E-4ED6-8835-93A1E18BE2BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="59" documentId="13_ncr:1_{AB1CBD6F-272E-4ED6-8835-93A1E18BE2BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D64E9C9-9596-4FD5-8A9E-89AA5C4371DC}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D4F34921-D08F-4BAD-B6B0-3F60A59243DD}"/>
   </bookViews>
@@ -662,6 +662,12 @@
       <c r="C11" t="s">
         <v>6</v>
       </c>
+      <c r="D11">
+        <v>42</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
@@ -673,6 +679,12 @@
       <c r="C12" t="s">
         <v>6</v>
       </c>
+      <c r="D12">
+        <v>47</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
@@ -684,6 +696,12 @@
       <c r="C13" t="s">
         <v>6</v>
       </c>
+      <c r="D13">
+        <v>71</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
@@ -695,6 +713,12 @@
       <c r="C14" t="s">
         <v>6</v>
       </c>
+      <c r="D14">
+        <v>98</v>
+      </c>
+      <c r="E14">
+        <v>5</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
@@ -706,6 +730,12 @@
       <c r="C15" t="s">
         <v>6</v>
       </c>
+      <c r="D15">
+        <v>74</v>
+      </c>
+      <c r="E15">
+        <v>2</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
@@ -717,6 +747,12 @@
       <c r="C16" t="s">
         <v>6</v>
       </c>
+      <c r="D16">
+        <v>65</v>
+      </c>
+      <c r="E16">
+        <v>3</v>
+      </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
@@ -728,6 +764,12 @@
       <c r="C17" t="s">
         <v>6</v>
       </c>
+      <c r="D17">
+        <v>68</v>
+      </c>
+      <c r="E17">
+        <v>6</v>
+      </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
@@ -739,6 +781,12 @@
       <c r="C18" t="s">
         <v>6</v>
       </c>
+      <c r="D18">
+        <v>49</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
@@ -750,6 +798,12 @@
       <c r="C19" t="s">
         <v>6</v>
       </c>
+      <c r="D19">
+        <v>48</v>
+      </c>
+      <c r="E19">
+        <v>8</v>
+      </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
@@ -761,6 +815,12 @@
       <c r="C20" t="s">
         <v>6</v>
       </c>
+      <c r="D20">
+        <v>88</v>
+      </c>
+      <c r="E20">
+        <v>2</v>
+      </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
@@ -1129,6 +1189,12 @@
       <c r="C42" t="s">
         <v>6</v>
       </c>
+      <c r="D42">
+        <v>73</v>
+      </c>
+      <c r="E42">
+        <v>34</v>
+      </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
@@ -1140,6 +1206,12 @@
       <c r="C43" t="s">
         <v>6</v>
       </c>
+      <c r="D43">
+        <v>93</v>
+      </c>
+      <c r="E43">
+        <v>43</v>
+      </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
@@ -1151,6 +1223,12 @@
       <c r="C44" t="s">
         <v>6</v>
       </c>
+      <c r="D44">
+        <v>83</v>
+      </c>
+      <c r="E44">
+        <v>29</v>
+      </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
@@ -1162,6 +1240,12 @@
       <c r="C45" t="s">
         <v>6</v>
       </c>
+      <c r="D45">
+        <v>91</v>
+      </c>
+      <c r="E45">
+        <v>43</v>
+      </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
@@ -1173,6 +1257,12 @@
       <c r="C46" t="s">
         <v>6</v>
       </c>
+      <c r="D46">
+        <v>90</v>
+      </c>
+      <c r="E46">
+        <v>45</v>
+      </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
@@ -1184,6 +1274,12 @@
       <c r="C47" t="s">
         <v>6</v>
       </c>
+      <c r="D47">
+        <v>53</v>
+      </c>
+      <c r="E47">
+        <v>36</v>
+      </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
@@ -1195,6 +1291,12 @@
       <c r="C48" t="s">
         <v>6</v>
       </c>
+      <c r="D48">
+        <v>38</v>
+      </c>
+      <c r="E48">
+        <v>20</v>
+      </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
@@ -1206,6 +1308,12 @@
       <c r="C49" t="s">
         <v>6</v>
       </c>
+      <c r="D49">
+        <v>75</v>
+      </c>
+      <c r="E49">
+        <v>38</v>
+      </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
@@ -1217,6 +1325,12 @@
       <c r="C50" t="s">
         <v>6</v>
       </c>
+      <c r="D50">
+        <v>38</v>
+      </c>
+      <c r="E50">
+        <v>21</v>
+      </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
@@ -1228,6 +1342,12 @@
       <c r="C51" t="s">
         <v>6</v>
       </c>
+      <c r="D51">
+        <v>68</v>
+      </c>
+      <c r="E51">
+        <v>40</v>
+      </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
@@ -1238,6 +1358,12 @@
       </c>
       <c r="C52" t="s">
         <v>6</v>
+      </c>
+      <c r="D52">
+        <v>123</v>
+      </c>
+      <c r="E52">
+        <v>59</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">

--- a/data/raw/Cell_Counts/Stra8_100nMRA/20250104_100nMRA_Stra8_Counts.xlsx
+++ b/data/raw/Cell_Counts/Stra8_100nMRA/20250104_100nMRA_Stra8_Counts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://umhealth-my.sharepoint.com/personal/kbonefas_med_umich_edu/Documents/Documents/KDM5C_Germ_Mechanism/data/raw/Cell_Counts/Stra8_100nMRA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="59" documentId="13_ncr:1_{AB1CBD6F-272E-4ED6-8835-93A1E18BE2BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D64E9C9-9596-4FD5-8A9E-89AA5C4371DC}"/>
+  <xr:revisionPtr revIDLastSave="99" documentId="13_ncr:1_{AB1CBD6F-272E-4ED6-8835-93A1E18BE2BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AAD2854C-ACF3-4106-83B6-62A4A5AB644F}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D4F34921-D08F-4BAD-B6B0-3F60A59243DD}"/>
+    <workbookView xWindow="4800" yWindow="120" windowWidth="14340" windowHeight="8890" xr2:uid="{D4F34921-D08F-4BAD-B6B0-3F60A59243DD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -157,6 +157,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1376,6 +1380,12 @@
       <c r="C53" t="s">
         <v>6</v>
       </c>
+      <c r="D53">
+        <v>77</v>
+      </c>
+      <c r="E53">
+        <v>27</v>
+      </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
@@ -1387,6 +1397,12 @@
       <c r="C54" t="s">
         <v>6</v>
       </c>
+      <c r="D54">
+        <v>55</v>
+      </c>
+      <c r="E54">
+        <v>40</v>
+      </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
@@ -1398,6 +1414,12 @@
       <c r="C55" t="s">
         <v>6</v>
       </c>
+      <c r="D55">
+        <v>111</v>
+      </c>
+      <c r="E55">
+        <v>47</v>
+      </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
@@ -1409,6 +1431,12 @@
       <c r="C56" t="s">
         <v>6</v>
       </c>
+      <c r="D56">
+        <v>70</v>
+      </c>
+      <c r="E56">
+        <v>53</v>
+      </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
@@ -1420,6 +1448,12 @@
       <c r="C57" t="s">
         <v>6</v>
       </c>
+      <c r="D57">
+        <v>126</v>
+      </c>
+      <c r="E57">
+        <v>69</v>
+      </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
@@ -1431,6 +1465,12 @@
       <c r="C58" t="s">
         <v>6</v>
       </c>
+      <c r="D58">
+        <v>73</v>
+      </c>
+      <c r="E58">
+        <v>31</v>
+      </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
@@ -1442,6 +1482,12 @@
       <c r="C59" t="s">
         <v>6</v>
       </c>
+      <c r="D59">
+        <v>87</v>
+      </c>
+      <c r="E59">
+        <v>36</v>
+      </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
@@ -1453,6 +1499,12 @@
       <c r="C60" t="s">
         <v>6</v>
       </c>
+      <c r="D60">
+        <v>89</v>
+      </c>
+      <c r="E60">
+        <v>48</v>
+      </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
@@ -1464,6 +1516,12 @@
       <c r="C61" t="s">
         <v>6</v>
       </c>
+      <c r="D61">
+        <v>40</v>
+      </c>
+      <c r="E61">
+        <v>22</v>
+      </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
@@ -1611,6 +1669,12 @@
       <c r="C70" t="s">
         <v>6</v>
       </c>
+      <c r="D70">
+        <v>57</v>
+      </c>
+      <c r="E70">
+        <v>35</v>
+      </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
@@ -1622,6 +1686,12 @@
       <c r="C71" t="s">
         <v>6</v>
       </c>
+      <c r="D71">
+        <v>81</v>
+      </c>
+      <c r="E71">
+        <v>31</v>
+      </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
@@ -1633,6 +1703,12 @@
       <c r="C72" t="s">
         <v>6</v>
       </c>
+      <c r="D72">
+        <v>34</v>
+      </c>
+      <c r="E72">
+        <v>10</v>
+      </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
@@ -1763,6 +1839,12 @@
       <c r="C80" t="s">
         <v>6</v>
       </c>
+      <c r="D80">
+        <v>104</v>
+      </c>
+      <c r="E80">
+        <v>46</v>
+      </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
@@ -1774,6 +1856,12 @@
       <c r="C81" t="s">
         <v>6</v>
       </c>
+      <c r="D81">
+        <v>87</v>
+      </c>
+      <c r="E81">
+        <v>43</v>
+      </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
@@ -1785,6 +1873,12 @@
       <c r="C82" t="s">
         <v>6</v>
       </c>
+      <c r="D82">
+        <v>28</v>
+      </c>
+      <c r="E82">
+        <v>19</v>
+      </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
@@ -2901,6 +2995,12 @@
       <c r="C148" t="s">
         <v>19</v>
       </c>
+      <c r="D148">
+        <v>39</v>
+      </c>
+      <c r="E148">
+        <v>1</v>
+      </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
@@ -2912,6 +3012,12 @@
       <c r="C149" t="s">
         <v>19</v>
       </c>
+      <c r="D149">
+        <v>53</v>
+      </c>
+      <c r="E149">
+        <v>0</v>
+      </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
@@ -2923,6 +3029,12 @@
       <c r="C150" t="s">
         <v>19</v>
       </c>
+      <c r="D150">
+        <v>70</v>
+      </c>
+      <c r="E150">
+        <v>0</v>
+      </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
@@ -2933,6 +3045,12 @@
       </c>
       <c r="C151" t="s">
         <v>19</v>
+      </c>
+      <c r="D151">
+        <v>58</v>
+      </c>
+      <c r="E151">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/Cell_Counts/Stra8_100nMRA/20250104_100nMRA_Stra8_Counts.xlsx
+++ b/data/raw/Cell_Counts/Stra8_100nMRA/20250104_100nMRA_Stra8_Counts.xlsx
@@ -1,12 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://umhealth-my.sharepoint.com/personal/kbonefas_med_umich_edu/Documents/Documents/KDM5C_Germ_Mechanism/data/raw/Cell_Counts/Stra8_100nMRA/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="34" documentId="11_0BC45352537CA7203223AC7A047C39C11F3F42F9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CBE974E-9909-4A00-A0AD-980BF7F11FB6}"/>
+  <bookViews>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="ZUbPQ5Afb+ox1EZsiwzz9s1eG67WEz8oFAzhVoXuM7Q="/>
@@ -16,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="24">
   <si>
     <t>Sample</t>
   </si>
@@ -86,24 +95,29 @@
   <si>
     <t>D4</t>
   </si>
+  <si>
+    <t>C4</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -113,37 +127,45 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -333,20 +355,20 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G1000"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col customWidth="1" min="1" max="26" width="8.63"/>
+    <col min="1" max="26" width="8.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1">
+    <row r="1" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -366,3859 +388,4052 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="14.25" customHeight="1">
+    <row r="2" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="1">
-        <v>115.0</v>
+        <v>115</v>
       </c>
       <c r="E2" s="1">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" ht="14.25" customHeight="1">
+      <c r="G2" s="3"/>
+    </row>
+    <row r="3" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D3" s="1">
-        <v>59.0</v>
+        <v>59</v>
       </c>
       <c r="E3" s="1">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" ht="14.25" customHeight="1">
+    <row r="4" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D4" s="1">
-        <v>77.0</v>
+        <v>77</v>
       </c>
       <c r="E4" s="1">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" ht="14.25" customHeight="1">
+    <row r="5" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D5" s="1">
-        <v>91.0</v>
+        <v>91</v>
       </c>
       <c r="E5" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" ht="14.25" customHeight="1">
+    <row r="6" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D6" s="1">
-        <v>59.0</v>
+        <v>59</v>
       </c>
       <c r="E6" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" ht="14.25" customHeight="1">
+    <row r="7" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="1">
-        <v>94.0</v>
+        <v>94</v>
       </c>
       <c r="E7" s="1">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" ht="14.25" customHeight="1">
+    <row r="8" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="1">
-        <v>68.0</v>
+        <v>68</v>
       </c>
       <c r="E8" s="1">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" ht="14.25" customHeight="1">
+    <row r="9" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D9" s="1">
-        <v>94.0</v>
+        <v>94</v>
       </c>
       <c r="E9" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" ht="14.25" customHeight="1">
+    <row r="10" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B10" s="1">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D10" s="1">
-        <v>68.0</v>
+        <v>68</v>
       </c>
       <c r="E10" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" ht="14.25" customHeight="1">
+    <row r="11" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D11" s="1">
-        <v>42.0</v>
+        <v>42</v>
       </c>
       <c r="E11" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" ht="14.25" customHeight="1">
+    <row r="12" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B12" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="1">
-        <v>47.0</v>
+        <v>47</v>
       </c>
       <c r="E12" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" ht="14.25" customHeight="1">
+    <row r="13" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B13" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D13" s="1">
-        <v>71.0</v>
+        <v>71</v>
       </c>
       <c r="E13" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="14" ht="14.25" customHeight="1">
+    <row r="14" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B14" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D14" s="1">
-        <v>98.0</v>
+        <v>98</v>
       </c>
       <c r="E14" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" ht="14.25" customHeight="1">
+    <row r="15" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B15" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D15" s="1">
-        <v>74.0</v>
+        <v>74</v>
       </c>
       <c r="E15" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="16" ht="14.25" customHeight="1">
+    <row r="16" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B16" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D16" s="1">
-        <v>65.0</v>
+        <v>65</v>
       </c>
       <c r="E16" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="17" ht="14.25" customHeight="1">
+    <row r="17" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B17" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D17" s="1">
-        <v>68.0</v>
+        <v>68</v>
       </c>
       <c r="E17" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="18" ht="14.25" customHeight="1">
+    <row r="18" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B18" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D18" s="1">
-        <v>49.0</v>
+        <v>49</v>
       </c>
       <c r="E18" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="19" ht="14.25" customHeight="1">
+    <row r="19" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B19" s="1">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D19" s="1">
-        <v>48.0</v>
+        <v>48</v>
       </c>
       <c r="E19" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="20" ht="14.25" customHeight="1">
+    <row r="20" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B20" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D20" s="1">
-        <v>88.0</v>
+        <v>88</v>
       </c>
       <c r="E20" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="21" ht="14.25" customHeight="1">
+    <row r="21" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B21" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D21" s="1">
-        <v>44.0</v>
+        <v>44</v>
       </c>
       <c r="E21" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="22" ht="14.25" customHeight="1">
+    <row r="22" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B22" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D22" s="1">
-        <v>52.0</v>
+        <v>52</v>
       </c>
       <c r="E22" s="1">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="23" ht="14.25" customHeight="1">
+    <row r="23" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B23" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D23" s="1">
-        <v>89.0</v>
+        <v>89</v>
       </c>
       <c r="E23" s="1">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="24" ht="14.25" customHeight="1">
+    <row r="24" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B24" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D24" s="1">
-        <v>69.0</v>
+        <v>69</v>
       </c>
       <c r="E24" s="1">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="25" ht="14.25" customHeight="1">
+    <row r="25" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B25" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D25" s="1">
-        <v>71.0</v>
+        <v>71</v>
       </c>
       <c r="E25" s="1">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="26" ht="14.25" customHeight="1">
+    <row r="26" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B26" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D26" s="1">
-        <v>62.0</v>
+        <v>62</v>
       </c>
       <c r="E26" s="1">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="27" ht="14.25" customHeight="1">
+    <row r="27" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B27" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D27" s="1">
-        <v>82.0</v>
+        <v>82</v>
       </c>
       <c r="E27" s="1">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="28" ht="14.25" customHeight="1">
+    <row r="28" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B28" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D28" s="1">
-        <v>64.0</v>
+        <v>64</v>
       </c>
       <c r="E28" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="29" ht="14.25" customHeight="1">
+    <row r="29" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B29" s="1">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D29" s="1">
-        <v>53.0</v>
+        <v>53</v>
       </c>
       <c r="E29" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="30" ht="14.25" customHeight="1">
+    <row r="30" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B30" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D30" s="1">
-        <v>66.0</v>
+        <v>66</v>
       </c>
       <c r="E30" s="1">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="31" ht="14.25" customHeight="1">
+    <row r="31" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B31" s="1">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D31" s="1">
-        <v>74.0</v>
+        <v>74</v>
       </c>
       <c r="E31" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="32" ht="14.25" customHeight="1">
+    <row r="32" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B32" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D32" s="1">
-        <v>90.0</v>
+        <v>90</v>
       </c>
       <c r="E32" s="1">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="33" ht="14.25" customHeight="1">
+    <row r="33" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B33" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D33" s="1">
-        <v>73.0</v>
+        <v>73</v>
       </c>
       <c r="E33" s="1">
-        <v>29.0</v>
+        <v>29</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="34" ht="14.25" customHeight="1">
+    <row r="34" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B34" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D34" s="1">
-        <v>93.0</v>
+        <v>93</v>
       </c>
       <c r="E34" s="1">
-        <v>53.0</v>
+        <v>53</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="35" ht="14.25" customHeight="1">
+    <row r="35" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B35" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D35" s="1">
-        <v>82.0</v>
+        <v>82</v>
       </c>
       <c r="E35" s="1">
-        <v>44.0</v>
+        <v>44</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="36" ht="14.25" customHeight="1">
+    <row r="36" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B36" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D36" s="1">
-        <v>51.0</v>
+        <v>51</v>
       </c>
       <c r="E36" s="1">
-        <v>27.0</v>
+        <v>27</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="37" ht="14.25" customHeight="1">
+    <row r="37" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B37" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D37" s="1">
-        <v>69.0</v>
+        <v>69</v>
       </c>
       <c r="E37" s="1">
-        <v>47.0</v>
+        <v>47</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="38" ht="14.25" customHeight="1">
+    <row r="38" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B38" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D38" s="1">
-        <v>38.0</v>
+        <v>38</v>
       </c>
       <c r="E38" s="1">
-        <v>34.0</v>
+        <v>34</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="39" ht="14.25" customHeight="1">
+    <row r="39" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B39" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D39" s="1">
-        <v>110.0</v>
+        <v>110</v>
       </c>
       <c r="E39" s="1">
-        <v>71.0</v>
+        <v>71</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="40" ht="14.25" customHeight="1">
+    <row r="40" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B40" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D40" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="E40" s="1">
-        <v>61.0</v>
+        <v>61</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="41" ht="14.25" customHeight="1">
+    <row r="41" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B41" s="1">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D41" s="1">
-        <v>92.0</v>
+        <v>92</v>
       </c>
       <c r="E41" s="1">
-        <v>48.0</v>
+        <v>48</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="42" ht="14.25" customHeight="1">
+    <row r="42" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B42" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D42" s="1">
-        <v>73.0</v>
+        <v>73</v>
       </c>
       <c r="E42" s="1">
-        <v>34.0</v>
+        <v>34</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="43" ht="14.25" customHeight="1">
+    <row r="43" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B43" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D43" s="1">
-        <v>93.0</v>
+        <v>93</v>
       </c>
       <c r="E43" s="1">
-        <v>43.0</v>
+        <v>43</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="44" ht="14.25" customHeight="1">
+    <row r="44" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B44" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D44" s="1">
-        <v>83.0</v>
+        <v>83</v>
       </c>
       <c r="E44" s="1">
-        <v>29.0</v>
+        <v>29</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="45" ht="14.25" customHeight="1">
+    <row r="45" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B45" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D45" s="1">
-        <v>91.0</v>
+        <v>91</v>
       </c>
       <c r="E45" s="1">
-        <v>43.0</v>
+        <v>43</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="46" ht="14.25" customHeight="1">
+    <row r="46" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B46" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D46" s="1">
-        <v>90.0</v>
+        <v>90</v>
       </c>
       <c r="E46" s="1">
-        <v>45.0</v>
+        <v>45</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="47" ht="14.25" customHeight="1">
+    <row r="47" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B47" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D47" s="1">
-        <v>53.0</v>
+        <v>53</v>
       </c>
       <c r="E47" s="1">
-        <v>36.0</v>
+        <v>36</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="48" ht="14.25" customHeight="1">
+    <row r="48" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B48" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D48" s="1">
-        <v>38.0</v>
+        <v>38</v>
       </c>
       <c r="E48" s="1">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="49" ht="14.25" customHeight="1">
+    <row r="49" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B49" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D49" s="1">
-        <v>75.0</v>
+        <v>75</v>
       </c>
       <c r="E49" s="1">
-        <v>38.0</v>
+        <v>38</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="50" ht="14.25" customHeight="1">
+    <row r="50" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B50" s="1">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D50" s="1">
-        <v>38.0</v>
+        <v>38</v>
       </c>
       <c r="E50" s="1">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="51" ht="14.25" customHeight="1">
+    <row r="51" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B51" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D51" s="1">
-        <v>68.0</v>
+        <v>68</v>
       </c>
       <c r="E51" s="1">
-        <v>40.0</v>
+        <v>40</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="52" ht="14.25" customHeight="1">
+    <row r="52" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B52" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D52" s="1">
-        <v>123.0</v>
+        <v>123</v>
       </c>
       <c r="E52" s="1">
-        <v>59.0</v>
+        <v>59</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="53" ht="14.25" customHeight="1">
+    <row r="53" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B53" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D53" s="1">
-        <v>77.0</v>
+        <v>77</v>
       </c>
       <c r="E53" s="1">
-        <v>27.0</v>
+        <v>27</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="54" ht="14.25" customHeight="1">
+    <row r="54" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B54" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D54" s="1">
-        <v>55.0</v>
+        <v>55</v>
       </c>
       <c r="E54" s="1">
-        <v>40.0</v>
+        <v>40</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="55" ht="14.25" customHeight="1">
+    <row r="55" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B55" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D55" s="1">
-        <v>111.0</v>
+        <v>111</v>
       </c>
       <c r="E55" s="1">
-        <v>47.0</v>
+        <v>47</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="56" ht="14.25" customHeight="1">
+    <row r="56" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B56" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D56" s="1">
-        <v>70.0</v>
+        <v>70</v>
       </c>
       <c r="E56" s="1">
-        <v>53.0</v>
+        <v>53</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="57" ht="14.25" customHeight="1">
+    <row r="57" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B57" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D57" s="1">
-        <v>126.0</v>
+        <v>126</v>
       </c>
       <c r="E57" s="1">
-        <v>69.0</v>
+        <v>69</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="58" ht="14.25" customHeight="1">
+    <row r="58" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B58" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D58" s="1">
-        <v>73.0</v>
+        <v>73</v>
       </c>
       <c r="E58" s="1">
-        <v>31.0</v>
+        <v>31</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="59" ht="14.25" customHeight="1">
+    <row r="59" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B59" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D59" s="1">
-        <v>87.0</v>
+        <v>87</v>
       </c>
       <c r="E59" s="1">
-        <v>36.0</v>
+        <v>36</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="60" ht="14.25" customHeight="1">
+    <row r="60" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B60" s="1">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D60" s="1">
-        <v>89.0</v>
+        <v>89</v>
       </c>
       <c r="E60" s="1">
-        <v>48.0</v>
+        <v>48</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="61" ht="14.25" customHeight="1">
+    <row r="61" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B61" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D61" s="1">
-        <v>40.0</v>
+        <v>40</v>
       </c>
       <c r="E61" s="1">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="62" ht="14.25" customHeight="1">
+    <row r="62" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B62" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D62" s="1">
-        <v>77.0</v>
+        <v>77</v>
       </c>
       <c r="E62" s="1">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="63" ht="14.25" customHeight="1">
+    <row r="63" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B63" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D63" s="1">
-        <v>105.0</v>
+        <v>105</v>
       </c>
       <c r="E63" s="1">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="64" ht="14.25" customHeight="1">
+    <row r="64" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B64" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D64" s="1">
-        <v>84.0</v>
+        <v>84</v>
       </c>
       <c r="E64" s="1">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="65" ht="14.25" customHeight="1">
+    <row r="65" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B65" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D65" s="1">
-        <v>68.0</v>
+        <v>68</v>
       </c>
       <c r="E65" s="1">
-        <v>13.0</v>
+        <v>13</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="66" ht="14.25" customHeight="1">
+    <row r="66" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B66" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D66" s="1">
-        <v>86.0</v>
+        <v>86</v>
       </c>
       <c r="E66" s="1">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="67" ht="14.25" customHeight="1">
+    <row r="67" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B67" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D67" s="1">
-        <v>82.0</v>
+        <v>82</v>
       </c>
       <c r="E67" s="1">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="68" ht="14.25" customHeight="1">
+    <row r="68" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B68" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D68" s="1">
-        <v>83.0</v>
+        <v>83</v>
       </c>
       <c r="E68" s="1">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="69" ht="14.25" customHeight="1">
+    <row r="69" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B69" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D69" s="1">
-        <v>99.0</v>
+        <v>99</v>
       </c>
       <c r="E69" s="1">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="70" ht="14.25" customHeight="1">
+    <row r="70" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B70" s="1">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D70" s="1">
-        <v>57.0</v>
+        <v>57</v>
       </c>
       <c r="E70" s="1">
-        <v>35.0</v>
+        <v>35</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="71" ht="14.25" customHeight="1">
+    <row r="71" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B71" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D71" s="1">
-        <v>81.0</v>
+        <v>81</v>
       </c>
       <c r="E71" s="1">
-        <v>31.0</v>
+        <v>31</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="72" ht="14.25" customHeight="1">
+    <row r="72" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B72" s="1">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D72" s="1">
-        <v>34.0</v>
+        <v>34</v>
       </c>
       <c r="E72" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="73" ht="14.25" customHeight="1">
+    <row r="73" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B73" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D73" s="1">
-        <v>108.0</v>
+        <v>108</v>
       </c>
       <c r="E73" s="1">
-        <v>38.0</v>
+        <v>38</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="74" ht="14.25" customHeight="1">
+    <row r="74" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B74" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D74" s="1">
-        <v>81.0</v>
+        <v>81</v>
       </c>
       <c r="E74" s="1">
-        <v>27.0</v>
+        <v>27</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="75" ht="14.25" customHeight="1">
+    <row r="75" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B75" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D75" s="1">
-        <v>45.0</v>
+        <v>45</v>
       </c>
       <c r="E75" s="1">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="76" ht="14.25" customHeight="1">
+    <row r="76" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B76" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D76" s="1">
-        <v>56.0</v>
+        <v>56</v>
       </c>
       <c r="E76" s="1">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="77" ht="14.25" customHeight="1">
+    <row r="77" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B77" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D77" s="1">
-        <v>76.0</v>
+        <v>76</v>
       </c>
       <c r="E77" s="1">
-        <v>34.0</v>
+        <v>34</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="78" ht="14.25" customHeight="1">
+    <row r="78" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B78" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D78" s="1">
-        <v>83.0</v>
+        <v>83</v>
       </c>
       <c r="E78" s="1">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="79" ht="14.25" customHeight="1">
+    <row r="79" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B79" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D79" s="1">
-        <v>94.0</v>
+        <v>94</v>
       </c>
       <c r="E79" s="1">
-        <v>29.0</v>
+        <v>29</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="80" ht="14.25" customHeight="1">
+    <row r="80" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B80" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D80" s="1">
-        <v>104.0</v>
+        <v>104</v>
       </c>
       <c r="E80" s="1">
-        <v>46.0</v>
+        <v>46</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="81" ht="14.25" customHeight="1">
+    <row r="81" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B81" s="1">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D81" s="1">
-        <v>87.0</v>
+        <v>87</v>
       </c>
       <c r="E81" s="1">
-        <v>43.0</v>
+        <v>43</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="82" ht="14.25" customHeight="1">
+    <row r="82" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B82" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D82" s="1">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="E82" s="1">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="83" ht="14.25" customHeight="1">
+    <row r="83" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B83" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D83" s="1">
-        <v>119.0</v>
+        <v>119</v>
       </c>
       <c r="E83" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="84" ht="14.25" customHeight="1">
+    <row r="84" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B84" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D84" s="1">
-        <v>46.0</v>
+        <v>46</v>
       </c>
       <c r="E84" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="85" ht="14.25" customHeight="1">
+    <row r="85" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B85" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D85" s="1">
-        <v>54.0</v>
+        <v>54</v>
       </c>
       <c r="E85" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="86" ht="14.25" customHeight="1">
+    <row r="86" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B86" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D86" s="1">
-        <v>43.0</v>
+        <v>43</v>
       </c>
       <c r="E86" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="87" ht="14.25" customHeight="1">
+    <row r="87" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B87" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D87" s="1">
-        <v>82.0</v>
+        <v>82</v>
       </c>
       <c r="E87" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="88" ht="14.25" customHeight="1">
+    <row r="88" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B88" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D88" s="1">
-        <v>65.0</v>
+        <v>65</v>
       </c>
       <c r="E88" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="89" ht="14.25" customHeight="1">
+    <row r="89" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B89" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D89" s="1">
-        <v>63.0</v>
+        <v>63</v>
       </c>
       <c r="E89" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="90" ht="14.25" customHeight="1">
+    <row r="90" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B90" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D90" s="1">
-        <v>71.0</v>
+        <v>71</v>
       </c>
       <c r="E90" s="1">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="91" ht="14.25" customHeight="1">
+    <row r="91" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B91" s="1">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D91" s="1">
-        <v>46.0</v>
+        <v>46</v>
       </c>
       <c r="E91" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="92" ht="14.25" customHeight="1">
+    <row r="92" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B92" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D92" s="1">
-        <v>62.0</v>
+        <v>62</v>
       </c>
       <c r="E92" s="1">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="93" ht="14.25" customHeight="1">
+    <row r="93" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B93" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D93" s="1">
-        <v>64.0</v>
+        <v>64</v>
       </c>
       <c r="E93" s="1">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="94" ht="14.25" customHeight="1">
+    <row r="94" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B94" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D94" s="1">
-        <v>48.0</v>
+        <v>48</v>
       </c>
       <c r="E94" s="1">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="95" ht="14.25" customHeight="1">
+    <row r="95" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B95" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D95" s="1">
-        <v>85.0</v>
+        <v>85</v>
       </c>
       <c r="E95" s="1">
-        <v>26.0</v>
+        <v>26</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="96" ht="14.25" customHeight="1">
+    <row r="96" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B96" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D96" s="1">
-        <v>89.0</v>
+        <v>89</v>
       </c>
       <c r="E96" s="1">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="97" ht="14.25" customHeight="1">
+    <row r="97" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B97" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D97" s="1">
-        <v>73.0</v>
+        <v>73</v>
       </c>
       <c r="E97" s="1">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="98" ht="14.25" customHeight="1">
+    <row r="98" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B98" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D98" s="1">
-        <v>86.0</v>
+        <v>86</v>
       </c>
       <c r="E98" s="1">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="99" ht="14.25" customHeight="1">
+    <row r="99" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B99" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D99" s="1">
-        <v>49.0</v>
+        <v>49</v>
       </c>
       <c r="E99" s="1">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="100" ht="14.25" customHeight="1">
+    <row r="100" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B100" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D100" s="1">
-        <v>73.0</v>
+        <v>73</v>
       </c>
       <c r="E100" s="1">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="101" ht="14.25" customHeight="1">
+    <row r="101" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B101" s="1">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D101" s="1">
-        <v>56.0</v>
+        <v>56</v>
       </c>
       <c r="E101" s="1">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="102" ht="14.25" customHeight="1">
+    <row r="102" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B102" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D102" s="1">
-        <v>91.0</v>
+        <v>91</v>
       </c>
       <c r="E102" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="103" ht="14.25" customHeight="1">
+    <row r="103" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B103" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D103" s="1">
-        <v>54.0</v>
+        <v>54</v>
       </c>
       <c r="E103" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="104" ht="14.25" customHeight="1">
+    <row r="104" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B104" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D104" s="1">
-        <v>102.0</v>
+        <v>102</v>
       </c>
       <c r="E104" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="105" ht="14.25" customHeight="1">
+    <row r="105" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B105" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D105" s="1">
-        <v>75.0</v>
+        <v>75</v>
       </c>
       <c r="E105" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="106" ht="14.25" customHeight="1">
+    <row r="106" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B106" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D106" s="1">
-        <v>77.0</v>
+        <v>77</v>
       </c>
       <c r="E106" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="107" ht="14.25" customHeight="1">
+    <row r="107" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B107" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D107" s="1">
-        <v>76.0</v>
+        <v>76</v>
       </c>
       <c r="E107" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="108" ht="14.25" customHeight="1">
+    <row r="108" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B108" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D108" s="1">
-        <v>117.0</v>
+        <v>117</v>
       </c>
       <c r="E108" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="109" ht="14.25" customHeight="1">
+    <row r="109" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B109" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D109" s="1">
-        <v>75.0</v>
+        <v>75</v>
       </c>
       <c r="E109" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="110" ht="14.25" customHeight="1">
+    <row r="110" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B110" s="1">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D110" s="1">
-        <v>76.0</v>
+        <v>76</v>
       </c>
       <c r="E110" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="111" ht="14.25" customHeight="1">
+    <row r="111" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B111" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D111" s="1">
-        <v>144.0</v>
+        <v>144</v>
       </c>
       <c r="E111" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="112" ht="14.25" customHeight="1">
+    <row r="112" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B112" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D112" s="1">
-        <v>90.0</v>
+        <v>90</v>
       </c>
       <c r="E112" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="113" ht="14.25" customHeight="1">
+    <row r="113" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B113" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D113" s="1">
-        <v>112.0</v>
+        <v>112</v>
       </c>
       <c r="E113" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="114" ht="14.25" customHeight="1">
+    <row r="114" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B114" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D114" s="1">
-        <v>91.0</v>
+        <v>91</v>
       </c>
       <c r="E114" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="115" ht="14.25" customHeight="1">
+    <row r="115" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B115" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D115" s="1">
-        <v>103.0</v>
+        <v>103</v>
       </c>
       <c r="E115" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F115" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="116" ht="14.25" customHeight="1">
+    <row r="116" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B116" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D116" s="1">
-        <v>89.0</v>
+        <v>89</v>
       </c>
       <c r="E116" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="117" ht="14.25" customHeight="1">
+    <row r="117" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B117" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D117" s="1">
-        <v>44.0</v>
+        <v>44</v>
       </c>
       <c r="E117" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="118" ht="14.25" customHeight="1">
+    <row r="118" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B118" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D118" s="1">
-        <v>140.0</v>
+        <v>140</v>
       </c>
       <c r="E118" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="119" ht="14.25" customHeight="1">
+    <row r="119" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B119" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D119" s="1">
-        <v>146.0</v>
+        <v>146</v>
       </c>
       <c r="E119" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="120" ht="14.25" customHeight="1">
+    <row r="120" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B120" s="1">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D120" s="1">
-        <v>82.0</v>
+        <v>82</v>
       </c>
       <c r="E120" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="121" ht="14.25" customHeight="1">
+    <row r="121" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B121" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D121" s="1">
-        <v>45.0</v>
+        <v>45</v>
       </c>
       <c r="E121" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="122" ht="14.25" customHeight="1">
+    <row r="122" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B122" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D122" s="1">
-        <v>102.0</v>
+        <v>102</v>
       </c>
       <c r="E122" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="123" ht="14.25" customHeight="1">
+    <row r="123" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B123" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D123" s="1">
-        <v>126.0</v>
+        <v>126</v>
       </c>
       <c r="E123" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="124" ht="14.25" customHeight="1">
+    <row r="124" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B124" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D124" s="1">
-        <v>96.0</v>
+        <v>96</v>
       </c>
       <c r="E124" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="125" ht="14.25" customHeight="1">
+    <row r="125" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B125" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D125" s="1">
-        <v>106.0</v>
+        <v>106</v>
       </c>
       <c r="E125" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F125" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="126" ht="14.25" customHeight="1">
+    <row r="126" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B126" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D126" s="1">
-        <v>89.0</v>
+        <v>89</v>
       </c>
       <c r="E126" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F126" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="127" ht="14.25" customHeight="1">
+    <row r="127" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B127" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D127" s="1">
-        <v>99.0</v>
+        <v>99</v>
       </c>
       <c r="E127" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="128" ht="14.25" customHeight="1">
+    <row r="128" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B128" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D128" s="1">
-        <v>118.0</v>
+        <v>118</v>
       </c>
       <c r="E128" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F128" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="129" ht="14.25" customHeight="1">
+    <row r="129" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B129" s="1">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D129" s="1">
-        <v>164.0</v>
+        <v>164</v>
       </c>
       <c r="E129" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F129" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="130" ht="14.25" customHeight="1">
+    <row r="130" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B130" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D130" s="1">
-        <v>137.0</v>
+        <v>137</v>
       </c>
       <c r="E130" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F130" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="131" ht="14.25" customHeight="1">
+    <row r="131" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B131" s="1">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D131" s="1">
-        <v>116.0</v>
+        <v>116</v>
       </c>
       <c r="E131" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F131" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="132" ht="14.25" customHeight="1">
+    <row r="132" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B132" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D132" s="1">
-        <v>85.0</v>
+        <v>85</v>
       </c>
       <c r="E132" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F132" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="133" ht="14.25" customHeight="1">
+    <row r="133" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B133" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D133" s="1">
-        <v>76.0</v>
+        <v>76</v>
       </c>
       <c r="E133" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="134" ht="14.25" customHeight="1">
+    <row r="134" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B134" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D134" s="1">
-        <v>65.0</v>
+        <v>65</v>
       </c>
       <c r="E134" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="135" ht="14.25" customHeight="1">
+    <row r="135" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B135" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D135" s="1">
-        <v>91.0</v>
+        <v>91</v>
       </c>
       <c r="E135" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="136" ht="14.25" customHeight="1">
+    <row r="136" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B136" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D136" s="1">
-        <v>124.0</v>
+        <v>124</v>
       </c>
       <c r="E136" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F136" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="137" ht="14.25" customHeight="1">
+    <row r="137" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B137" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D137" s="1">
-        <v>56.0</v>
+        <v>56</v>
       </c>
       <c r="E137" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F137" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="138" ht="14.25" customHeight="1">
+    <row r="138" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B138" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D138" s="1">
-        <v>94.0</v>
+        <v>94</v>
       </c>
       <c r="E138" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F138" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="139" ht="14.25" customHeight="1">
+    <row r="139" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B139" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D139" s="1">
-        <v>122.0</v>
+        <v>122</v>
       </c>
       <c r="E139" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F139" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="140" ht="14.25" customHeight="1">
+    <row r="140" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B140" s="1">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D140" s="1">
-        <v>153.0</v>
+        <v>153</v>
       </c>
       <c r="E140" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F140" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="141" ht="14.25" customHeight="1">
+    <row r="141" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B141" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D141" s="1">
-        <v>94.0</v>
+        <v>94</v>
       </c>
       <c r="E141" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F141" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="142" ht="14.25" customHeight="1">
+    <row r="142" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B142" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D142" s="1">
-        <v>56.0</v>
+        <v>56</v>
       </c>
       <c r="E142" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F142" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="143" ht="14.25" customHeight="1">
+    <row r="143" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B143" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D143" s="1">
-        <v>95.0</v>
+        <v>95</v>
       </c>
       <c r="E143" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F143" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="144" ht="14.25" customHeight="1">
+    <row r="144" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B144" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D144" s="1">
-        <v>102.0</v>
+        <v>102</v>
       </c>
       <c r="E144" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F144" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="145" ht="14.25" customHeight="1">
+    <row r="145" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B145" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D145" s="1">
-        <v>134.0</v>
+        <v>134</v>
       </c>
       <c r="E145" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F145" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="146" ht="14.25" customHeight="1">
+    <row r="146" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B146" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D146" s="1">
-        <v>49.0</v>
+        <v>49</v>
       </c>
       <c r="E146" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F146" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="147" ht="14.25" customHeight="1">
+    <row r="147" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B147" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D147" s="1">
-        <v>45.0</v>
+        <v>45</v>
       </c>
       <c r="E147" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F147" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="148" ht="14.25" customHeight="1">
+    <row r="148" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B148" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D148" s="1">
-        <v>39.0</v>
+        <v>39</v>
       </c>
       <c r="E148" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F148" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="149" ht="14.25" customHeight="1">
+    <row r="149" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B149" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D149" s="1">
-        <v>53.0</v>
+        <v>53</v>
       </c>
       <c r="E149" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F149" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="150" ht="14.25" customHeight="1">
+    <row r="150" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B150" s="1">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D150" s="1">
-        <v>70.0</v>
+        <v>70</v>
       </c>
       <c r="E150" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F150" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="151" ht="14.25" customHeight="1">
+    <row r="151" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B151" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D151" s="1">
-        <v>58.0</v>
+        <v>58</v>
       </c>
       <c r="E151" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F151" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="152" ht="14.25" customHeight="1"/>
-    <row r="153" ht="14.25" customHeight="1"/>
-    <row r="154" ht="14.25" customHeight="1"/>
-    <row r="155" ht="14.25" customHeight="1"/>
-    <row r="156" ht="14.25" customHeight="1"/>
-    <row r="157" ht="14.25" customHeight="1"/>
-    <row r="158" ht="14.25" customHeight="1"/>
-    <row r="159" ht="14.25" customHeight="1"/>
-    <row r="160" ht="14.25" customHeight="1"/>
-    <row r="161" ht="14.25" customHeight="1"/>
-    <row r="162" ht="14.25" customHeight="1"/>
-    <row r="163" ht="14.25" customHeight="1"/>
-    <row r="164" ht="14.25" customHeight="1"/>
-    <row r="165" ht="14.25" customHeight="1"/>
-    <row r="166" ht="14.25" customHeight="1"/>
-    <row r="167" ht="14.25" customHeight="1"/>
-    <row r="168" ht="14.25" customHeight="1"/>
-    <row r="169" ht="14.25" customHeight="1"/>
-    <row r="170" ht="14.25" customHeight="1"/>
-    <row r="171" ht="14.25" customHeight="1"/>
-    <row r="172" ht="14.25" customHeight="1"/>
-    <row r="173" ht="14.25" customHeight="1"/>
-    <row r="174" ht="14.25" customHeight="1"/>
-    <row r="175" ht="14.25" customHeight="1"/>
-    <row r="176" ht="14.25" customHeight="1"/>
-    <row r="177" ht="14.25" customHeight="1"/>
-    <row r="178" ht="14.25" customHeight="1"/>
-    <row r="179" ht="14.25" customHeight="1"/>
-    <row r="180" ht="14.25" customHeight="1"/>
-    <row r="181" ht="14.25" customHeight="1"/>
-    <row r="182" ht="14.25" customHeight="1"/>
-    <row r="183" ht="14.25" customHeight="1"/>
-    <row r="184" ht="14.25" customHeight="1"/>
-    <row r="185" ht="14.25" customHeight="1"/>
-    <row r="186" ht="14.25" customHeight="1"/>
-    <row r="187" ht="14.25" customHeight="1"/>
-    <row r="188" ht="14.25" customHeight="1"/>
-    <row r="189" ht="14.25" customHeight="1"/>
-    <row r="190" ht="14.25" customHeight="1"/>
-    <row r="191" ht="14.25" customHeight="1"/>
-    <row r="192" ht="14.25" customHeight="1"/>
-    <row r="193" ht="14.25" customHeight="1"/>
-    <row r="194" ht="14.25" customHeight="1"/>
-    <row r="195" ht="14.25" customHeight="1"/>
-    <row r="196" ht="14.25" customHeight="1"/>
-    <row r="197" ht="14.25" customHeight="1"/>
-    <row r="198" ht="14.25" customHeight="1"/>
-    <row r="199" ht="14.25" customHeight="1"/>
-    <row r="200" ht="14.25" customHeight="1"/>
-    <row r="201" ht="14.25" customHeight="1"/>
-    <row r="202" ht="14.25" customHeight="1"/>
-    <row r="203" ht="14.25" customHeight="1"/>
-    <row r="204" ht="14.25" customHeight="1"/>
-    <row r="205" ht="14.25" customHeight="1"/>
-    <row r="206" ht="14.25" customHeight="1"/>
-    <row r="207" ht="14.25" customHeight="1"/>
-    <row r="208" ht="14.25" customHeight="1"/>
-    <row r="209" ht="14.25" customHeight="1"/>
-    <row r="210" ht="14.25" customHeight="1"/>
-    <row r="211" ht="14.25" customHeight="1"/>
-    <row r="212" ht="14.25" customHeight="1"/>
-    <row r="213" ht="14.25" customHeight="1"/>
-    <row r="214" ht="14.25" customHeight="1"/>
-    <row r="215" ht="14.25" customHeight="1"/>
-    <row r="216" ht="14.25" customHeight="1"/>
-    <row r="217" ht="14.25" customHeight="1"/>
-    <row r="218" ht="14.25" customHeight="1"/>
-    <row r="219" ht="14.25" customHeight="1"/>
-    <row r="220" ht="14.25" customHeight="1"/>
-    <row r="221" ht="14.25" customHeight="1"/>
-    <row r="222" ht="14.25" customHeight="1"/>
-    <row r="223" ht="14.25" customHeight="1"/>
-    <row r="224" ht="14.25" customHeight="1"/>
-    <row r="225" ht="14.25" customHeight="1"/>
-    <row r="226" ht="14.25" customHeight="1"/>
-    <row r="227" ht="14.25" customHeight="1"/>
-    <row r="228" ht="14.25" customHeight="1"/>
-    <row r="229" ht="14.25" customHeight="1"/>
-    <row r="230" ht="14.25" customHeight="1"/>
-    <row r="231" ht="14.25" customHeight="1"/>
-    <row r="232" ht="14.25" customHeight="1"/>
-    <row r="233" ht="14.25" customHeight="1"/>
-    <row r="234" ht="14.25" customHeight="1"/>
-    <row r="235" ht="14.25" customHeight="1"/>
-    <row r="236" ht="14.25" customHeight="1"/>
-    <row r="237" ht="14.25" customHeight="1"/>
-    <row r="238" ht="14.25" customHeight="1"/>
-    <row r="239" ht="14.25" customHeight="1"/>
-    <row r="240" ht="14.25" customHeight="1"/>
-    <row r="241" ht="14.25" customHeight="1"/>
-    <row r="242" ht="14.25" customHeight="1"/>
-    <row r="243" ht="14.25" customHeight="1"/>
-    <row r="244" ht="14.25" customHeight="1"/>
-    <row r="245" ht="14.25" customHeight="1"/>
-    <row r="246" ht="14.25" customHeight="1"/>
-    <row r="247" ht="14.25" customHeight="1"/>
-    <row r="248" ht="14.25" customHeight="1"/>
-    <row r="249" ht="14.25" customHeight="1"/>
-    <row r="250" ht="14.25" customHeight="1"/>
-    <row r="251" ht="14.25" customHeight="1"/>
-    <row r="252" ht="14.25" customHeight="1"/>
-    <row r="253" ht="14.25" customHeight="1"/>
-    <row r="254" ht="14.25" customHeight="1"/>
-    <row r="255" ht="14.25" customHeight="1"/>
-    <row r="256" ht="14.25" customHeight="1"/>
-    <row r="257" ht="14.25" customHeight="1"/>
-    <row r="258" ht="14.25" customHeight="1"/>
-    <row r="259" ht="14.25" customHeight="1"/>
-    <row r="260" ht="14.25" customHeight="1"/>
-    <row r="261" ht="14.25" customHeight="1"/>
-    <row r="262" ht="14.25" customHeight="1"/>
-    <row r="263" ht="14.25" customHeight="1"/>
-    <row r="264" ht="14.25" customHeight="1"/>
-    <row r="265" ht="14.25" customHeight="1"/>
-    <row r="266" ht="14.25" customHeight="1"/>
-    <row r="267" ht="14.25" customHeight="1"/>
-    <row r="268" ht="14.25" customHeight="1"/>
-    <row r="269" ht="14.25" customHeight="1"/>
-    <row r="270" ht="14.25" customHeight="1"/>
-    <row r="271" ht="14.25" customHeight="1"/>
-    <row r="272" ht="14.25" customHeight="1"/>
-    <row r="273" ht="14.25" customHeight="1"/>
-    <row r="274" ht="14.25" customHeight="1"/>
-    <row r="275" ht="14.25" customHeight="1"/>
-    <row r="276" ht="14.25" customHeight="1"/>
-    <row r="277" ht="14.25" customHeight="1"/>
-    <row r="278" ht="14.25" customHeight="1"/>
-    <row r="279" ht="14.25" customHeight="1"/>
-    <row r="280" ht="14.25" customHeight="1"/>
-    <row r="281" ht="14.25" customHeight="1"/>
-    <row r="282" ht="14.25" customHeight="1"/>
-    <row r="283" ht="14.25" customHeight="1"/>
-    <row r="284" ht="14.25" customHeight="1"/>
-    <row r="285" ht="14.25" customHeight="1"/>
-    <row r="286" ht="14.25" customHeight="1"/>
-    <row r="287" ht="14.25" customHeight="1"/>
-    <row r="288" ht="14.25" customHeight="1"/>
-    <row r="289" ht="14.25" customHeight="1"/>
-    <row r="290" ht="14.25" customHeight="1"/>
-    <row r="291" ht="14.25" customHeight="1"/>
-    <row r="292" ht="14.25" customHeight="1"/>
-    <row r="293" ht="14.25" customHeight="1"/>
-    <row r="294" ht="14.25" customHeight="1"/>
-    <row r="295" ht="14.25" customHeight="1"/>
-    <row r="296" ht="14.25" customHeight="1"/>
-    <row r="297" ht="14.25" customHeight="1"/>
-    <row r="298" ht="14.25" customHeight="1"/>
-    <row r="299" ht="14.25" customHeight="1"/>
-    <row r="300" ht="14.25" customHeight="1"/>
-    <row r="301" ht="14.25" customHeight="1"/>
-    <row r="302" ht="14.25" customHeight="1"/>
-    <row r="303" ht="14.25" customHeight="1"/>
-    <row r="304" ht="14.25" customHeight="1"/>
-    <row r="305" ht="14.25" customHeight="1"/>
-    <row r="306" ht="14.25" customHeight="1"/>
-    <row r="307" ht="14.25" customHeight="1"/>
-    <row r="308" ht="14.25" customHeight="1"/>
-    <row r="309" ht="14.25" customHeight="1"/>
-    <row r="310" ht="14.25" customHeight="1"/>
-    <row r="311" ht="14.25" customHeight="1"/>
-    <row r="312" ht="14.25" customHeight="1"/>
-    <row r="313" ht="14.25" customHeight="1"/>
-    <row r="314" ht="14.25" customHeight="1"/>
-    <row r="315" ht="14.25" customHeight="1"/>
-    <row r="316" ht="14.25" customHeight="1"/>
-    <row r="317" ht="14.25" customHeight="1"/>
-    <row r="318" ht="14.25" customHeight="1"/>
-    <row r="319" ht="14.25" customHeight="1"/>
-    <row r="320" ht="14.25" customHeight="1"/>
-    <row r="321" ht="14.25" customHeight="1"/>
-    <row r="322" ht="14.25" customHeight="1"/>
-    <row r="323" ht="14.25" customHeight="1"/>
-    <row r="324" ht="14.25" customHeight="1"/>
-    <row r="325" ht="14.25" customHeight="1"/>
-    <row r="326" ht="14.25" customHeight="1"/>
-    <row r="327" ht="14.25" customHeight="1"/>
-    <row r="328" ht="14.25" customHeight="1"/>
-    <row r="329" ht="14.25" customHeight="1"/>
-    <row r="330" ht="14.25" customHeight="1"/>
-    <row r="331" ht="14.25" customHeight="1"/>
-    <row r="332" ht="14.25" customHeight="1"/>
-    <row r="333" ht="14.25" customHeight="1"/>
-    <row r="334" ht="14.25" customHeight="1"/>
-    <row r="335" ht="14.25" customHeight="1"/>
-    <row r="336" ht="14.25" customHeight="1"/>
-    <row r="337" ht="14.25" customHeight="1"/>
-    <row r="338" ht="14.25" customHeight="1"/>
-    <row r="339" ht="14.25" customHeight="1"/>
-    <row r="340" ht="14.25" customHeight="1"/>
-    <row r="341" ht="14.25" customHeight="1"/>
-    <row r="342" ht="14.25" customHeight="1"/>
-    <row r="343" ht="14.25" customHeight="1"/>
-    <row r="344" ht="14.25" customHeight="1"/>
-    <row r="345" ht="14.25" customHeight="1"/>
-    <row r="346" ht="14.25" customHeight="1"/>
-    <row r="347" ht="14.25" customHeight="1"/>
-    <row r="348" ht="14.25" customHeight="1"/>
-    <row r="349" ht="14.25" customHeight="1"/>
-    <row r="350" ht="14.25" customHeight="1"/>
-    <row r="351" ht="14.25" customHeight="1"/>
-    <row r="352" ht="14.25" customHeight="1"/>
-    <row r="353" ht="14.25" customHeight="1"/>
-    <row r="354" ht="14.25" customHeight="1"/>
-    <row r="355" ht="14.25" customHeight="1"/>
-    <row r="356" ht="14.25" customHeight="1"/>
-    <row r="357" ht="14.25" customHeight="1"/>
-    <row r="358" ht="14.25" customHeight="1"/>
-    <row r="359" ht="14.25" customHeight="1"/>
-    <row r="360" ht="14.25" customHeight="1"/>
-    <row r="361" ht="14.25" customHeight="1"/>
-    <row r="362" ht="14.25" customHeight="1"/>
-    <row r="363" ht="14.25" customHeight="1"/>
-    <row r="364" ht="14.25" customHeight="1"/>
-    <row r="365" ht="14.25" customHeight="1"/>
-    <row r="366" ht="14.25" customHeight="1"/>
-    <row r="367" ht="14.25" customHeight="1"/>
-    <row r="368" ht="14.25" customHeight="1"/>
-    <row r="369" ht="14.25" customHeight="1"/>
-    <row r="370" ht="14.25" customHeight="1"/>
-    <row r="371" ht="14.25" customHeight="1"/>
-    <row r="372" ht="14.25" customHeight="1"/>
-    <row r="373" ht="14.25" customHeight="1"/>
-    <row r="374" ht="14.25" customHeight="1"/>
-    <row r="375" ht="14.25" customHeight="1"/>
-    <row r="376" ht="14.25" customHeight="1"/>
-    <row r="377" ht="14.25" customHeight="1"/>
-    <row r="378" ht="14.25" customHeight="1"/>
-    <row r="379" ht="14.25" customHeight="1"/>
-    <row r="380" ht="14.25" customHeight="1"/>
-    <row r="381" ht="14.25" customHeight="1"/>
-    <row r="382" ht="14.25" customHeight="1"/>
-    <row r="383" ht="14.25" customHeight="1"/>
-    <row r="384" ht="14.25" customHeight="1"/>
-    <row r="385" ht="14.25" customHeight="1"/>
-    <row r="386" ht="14.25" customHeight="1"/>
-    <row r="387" ht="14.25" customHeight="1"/>
-    <row r="388" ht="14.25" customHeight="1"/>
-    <row r="389" ht="14.25" customHeight="1"/>
-    <row r="390" ht="14.25" customHeight="1"/>
-    <row r="391" ht="14.25" customHeight="1"/>
-    <row r="392" ht="14.25" customHeight="1"/>
-    <row r="393" ht="14.25" customHeight="1"/>
-    <row r="394" ht="14.25" customHeight="1"/>
-    <row r="395" ht="14.25" customHeight="1"/>
-    <row r="396" ht="14.25" customHeight="1"/>
-    <row r="397" ht="14.25" customHeight="1"/>
-    <row r="398" ht="14.25" customHeight="1"/>
-    <row r="399" ht="14.25" customHeight="1"/>
-    <row r="400" ht="14.25" customHeight="1"/>
-    <row r="401" ht="14.25" customHeight="1"/>
-    <row r="402" ht="14.25" customHeight="1"/>
-    <row r="403" ht="14.25" customHeight="1"/>
-    <row r="404" ht="14.25" customHeight="1"/>
-    <row r="405" ht="14.25" customHeight="1"/>
-    <row r="406" ht="14.25" customHeight="1"/>
-    <row r="407" ht="14.25" customHeight="1"/>
-    <row r="408" ht="14.25" customHeight="1"/>
-    <row r="409" ht="14.25" customHeight="1"/>
-    <row r="410" ht="14.25" customHeight="1"/>
-    <row r="411" ht="14.25" customHeight="1"/>
-    <row r="412" ht="14.25" customHeight="1"/>
-    <row r="413" ht="14.25" customHeight="1"/>
-    <row r="414" ht="14.25" customHeight="1"/>
-    <row r="415" ht="14.25" customHeight="1"/>
-    <row r="416" ht="14.25" customHeight="1"/>
-    <row r="417" ht="14.25" customHeight="1"/>
-    <row r="418" ht="14.25" customHeight="1"/>
-    <row r="419" ht="14.25" customHeight="1"/>
-    <row r="420" ht="14.25" customHeight="1"/>
-    <row r="421" ht="14.25" customHeight="1"/>
-    <row r="422" ht="14.25" customHeight="1"/>
-    <row r="423" ht="14.25" customHeight="1"/>
-    <row r="424" ht="14.25" customHeight="1"/>
-    <row r="425" ht="14.25" customHeight="1"/>
-    <row r="426" ht="14.25" customHeight="1"/>
-    <row r="427" ht="14.25" customHeight="1"/>
-    <row r="428" ht="14.25" customHeight="1"/>
-    <row r="429" ht="14.25" customHeight="1"/>
-    <row r="430" ht="14.25" customHeight="1"/>
-    <row r="431" ht="14.25" customHeight="1"/>
-    <row r="432" ht="14.25" customHeight="1"/>
-    <row r="433" ht="14.25" customHeight="1"/>
-    <row r="434" ht="14.25" customHeight="1"/>
-    <row r="435" ht="14.25" customHeight="1"/>
-    <row r="436" ht="14.25" customHeight="1"/>
-    <row r="437" ht="14.25" customHeight="1"/>
-    <row r="438" ht="14.25" customHeight="1"/>
-    <row r="439" ht="14.25" customHeight="1"/>
-    <row r="440" ht="14.25" customHeight="1"/>
-    <row r="441" ht="14.25" customHeight="1"/>
-    <row r="442" ht="14.25" customHeight="1"/>
-    <row r="443" ht="14.25" customHeight="1"/>
-    <row r="444" ht="14.25" customHeight="1"/>
-    <row r="445" ht="14.25" customHeight="1"/>
-    <row r="446" ht="14.25" customHeight="1"/>
-    <row r="447" ht="14.25" customHeight="1"/>
-    <row r="448" ht="14.25" customHeight="1"/>
-    <row r="449" ht="14.25" customHeight="1"/>
-    <row r="450" ht="14.25" customHeight="1"/>
-    <row r="451" ht="14.25" customHeight="1"/>
-    <row r="452" ht="14.25" customHeight="1"/>
-    <row r="453" ht="14.25" customHeight="1"/>
-    <row r="454" ht="14.25" customHeight="1"/>
-    <row r="455" ht="14.25" customHeight="1"/>
-    <row r="456" ht="14.25" customHeight="1"/>
-    <row r="457" ht="14.25" customHeight="1"/>
-    <row r="458" ht="14.25" customHeight="1"/>
-    <row r="459" ht="14.25" customHeight="1"/>
-    <row r="460" ht="14.25" customHeight="1"/>
-    <row r="461" ht="14.25" customHeight="1"/>
-    <row r="462" ht="14.25" customHeight="1"/>
-    <row r="463" ht="14.25" customHeight="1"/>
-    <row r="464" ht="14.25" customHeight="1"/>
-    <row r="465" ht="14.25" customHeight="1"/>
-    <row r="466" ht="14.25" customHeight="1"/>
-    <row r="467" ht="14.25" customHeight="1"/>
-    <row r="468" ht="14.25" customHeight="1"/>
-    <row r="469" ht="14.25" customHeight="1"/>
-    <row r="470" ht="14.25" customHeight="1"/>
-    <row r="471" ht="14.25" customHeight="1"/>
-    <row r="472" ht="14.25" customHeight="1"/>
-    <row r="473" ht="14.25" customHeight="1"/>
-    <row r="474" ht="14.25" customHeight="1"/>
-    <row r="475" ht="14.25" customHeight="1"/>
-    <row r="476" ht="14.25" customHeight="1"/>
-    <row r="477" ht="14.25" customHeight="1"/>
-    <row r="478" ht="14.25" customHeight="1"/>
-    <row r="479" ht="14.25" customHeight="1"/>
-    <row r="480" ht="14.25" customHeight="1"/>
-    <row r="481" ht="14.25" customHeight="1"/>
-    <row r="482" ht="14.25" customHeight="1"/>
-    <row r="483" ht="14.25" customHeight="1"/>
-    <row r="484" ht="14.25" customHeight="1"/>
-    <row r="485" ht="14.25" customHeight="1"/>
-    <row r="486" ht="14.25" customHeight="1"/>
-    <row r="487" ht="14.25" customHeight="1"/>
-    <row r="488" ht="14.25" customHeight="1"/>
-    <row r="489" ht="14.25" customHeight="1"/>
-    <row r="490" ht="14.25" customHeight="1"/>
-    <row r="491" ht="14.25" customHeight="1"/>
-    <row r="492" ht="14.25" customHeight="1"/>
-    <row r="493" ht="14.25" customHeight="1"/>
-    <row r="494" ht="14.25" customHeight="1"/>
-    <row r="495" ht="14.25" customHeight="1"/>
-    <row r="496" ht="14.25" customHeight="1"/>
-    <row r="497" ht="14.25" customHeight="1"/>
-    <row r="498" ht="14.25" customHeight="1"/>
-    <row r="499" ht="14.25" customHeight="1"/>
-    <row r="500" ht="14.25" customHeight="1"/>
-    <row r="501" ht="14.25" customHeight="1"/>
-    <row r="502" ht="14.25" customHeight="1"/>
-    <row r="503" ht="14.25" customHeight="1"/>
-    <row r="504" ht="14.25" customHeight="1"/>
-    <row r="505" ht="14.25" customHeight="1"/>
-    <row r="506" ht="14.25" customHeight="1"/>
-    <row r="507" ht="14.25" customHeight="1"/>
-    <row r="508" ht="14.25" customHeight="1"/>
-    <row r="509" ht="14.25" customHeight="1"/>
-    <row r="510" ht="14.25" customHeight="1"/>
-    <row r="511" ht="14.25" customHeight="1"/>
-    <row r="512" ht="14.25" customHeight="1"/>
-    <row r="513" ht="14.25" customHeight="1"/>
-    <row r="514" ht="14.25" customHeight="1"/>
-    <row r="515" ht="14.25" customHeight="1"/>
-    <row r="516" ht="14.25" customHeight="1"/>
-    <row r="517" ht="14.25" customHeight="1"/>
-    <row r="518" ht="14.25" customHeight="1"/>
-    <row r="519" ht="14.25" customHeight="1"/>
-    <row r="520" ht="14.25" customHeight="1"/>
-    <row r="521" ht="14.25" customHeight="1"/>
-    <row r="522" ht="14.25" customHeight="1"/>
-    <row r="523" ht="14.25" customHeight="1"/>
-    <row r="524" ht="14.25" customHeight="1"/>
-    <row r="525" ht="14.25" customHeight="1"/>
-    <row r="526" ht="14.25" customHeight="1"/>
-    <row r="527" ht="14.25" customHeight="1"/>
-    <row r="528" ht="14.25" customHeight="1"/>
-    <row r="529" ht="14.25" customHeight="1"/>
-    <row r="530" ht="14.25" customHeight="1"/>
-    <row r="531" ht="14.25" customHeight="1"/>
-    <row r="532" ht="14.25" customHeight="1"/>
-    <row r="533" ht="14.25" customHeight="1"/>
-    <row r="534" ht="14.25" customHeight="1"/>
-    <row r="535" ht="14.25" customHeight="1"/>
-    <row r="536" ht="14.25" customHeight="1"/>
-    <row r="537" ht="14.25" customHeight="1"/>
-    <row r="538" ht="14.25" customHeight="1"/>
-    <row r="539" ht="14.25" customHeight="1"/>
-    <row r="540" ht="14.25" customHeight="1"/>
-    <row r="541" ht="14.25" customHeight="1"/>
-    <row r="542" ht="14.25" customHeight="1"/>
-    <row r="543" ht="14.25" customHeight="1"/>
-    <row r="544" ht="14.25" customHeight="1"/>
-    <row r="545" ht="14.25" customHeight="1"/>
-    <row r="546" ht="14.25" customHeight="1"/>
-    <row r="547" ht="14.25" customHeight="1"/>
-    <row r="548" ht="14.25" customHeight="1"/>
-    <row r="549" ht="14.25" customHeight="1"/>
-    <row r="550" ht="14.25" customHeight="1"/>
-    <row r="551" ht="14.25" customHeight="1"/>
-    <row r="552" ht="14.25" customHeight="1"/>
-    <row r="553" ht="14.25" customHeight="1"/>
-    <row r="554" ht="14.25" customHeight="1"/>
-    <row r="555" ht="14.25" customHeight="1"/>
-    <row r="556" ht="14.25" customHeight="1"/>
-    <row r="557" ht="14.25" customHeight="1"/>
-    <row r="558" ht="14.25" customHeight="1"/>
-    <row r="559" ht="14.25" customHeight="1"/>
-    <row r="560" ht="14.25" customHeight="1"/>
-    <row r="561" ht="14.25" customHeight="1"/>
-    <row r="562" ht="14.25" customHeight="1"/>
-    <row r="563" ht="14.25" customHeight="1"/>
-    <row r="564" ht="14.25" customHeight="1"/>
-    <row r="565" ht="14.25" customHeight="1"/>
-    <row r="566" ht="14.25" customHeight="1"/>
-    <row r="567" ht="14.25" customHeight="1"/>
-    <row r="568" ht="14.25" customHeight="1"/>
-    <row r="569" ht="14.25" customHeight="1"/>
-    <row r="570" ht="14.25" customHeight="1"/>
-    <row r="571" ht="14.25" customHeight="1"/>
-    <row r="572" ht="14.25" customHeight="1"/>
-    <row r="573" ht="14.25" customHeight="1"/>
-    <row r="574" ht="14.25" customHeight="1"/>
-    <row r="575" ht="14.25" customHeight="1"/>
-    <row r="576" ht="14.25" customHeight="1"/>
-    <row r="577" ht="14.25" customHeight="1"/>
-    <row r="578" ht="14.25" customHeight="1"/>
-    <row r="579" ht="14.25" customHeight="1"/>
-    <row r="580" ht="14.25" customHeight="1"/>
-    <row r="581" ht="14.25" customHeight="1"/>
-    <row r="582" ht="14.25" customHeight="1"/>
-    <row r="583" ht="14.25" customHeight="1"/>
-    <row r="584" ht="14.25" customHeight="1"/>
-    <row r="585" ht="14.25" customHeight="1"/>
-    <row r="586" ht="14.25" customHeight="1"/>
-    <row r="587" ht="14.25" customHeight="1"/>
-    <row r="588" ht="14.25" customHeight="1"/>
-    <row r="589" ht="14.25" customHeight="1"/>
-    <row r="590" ht="14.25" customHeight="1"/>
-    <row r="591" ht="14.25" customHeight="1"/>
-    <row r="592" ht="14.25" customHeight="1"/>
-    <row r="593" ht="14.25" customHeight="1"/>
-    <row r="594" ht="14.25" customHeight="1"/>
-    <row r="595" ht="14.25" customHeight="1"/>
-    <row r="596" ht="14.25" customHeight="1"/>
-    <row r="597" ht="14.25" customHeight="1"/>
-    <row r="598" ht="14.25" customHeight="1"/>
-    <row r="599" ht="14.25" customHeight="1"/>
-    <row r="600" ht="14.25" customHeight="1"/>
-    <row r="601" ht="14.25" customHeight="1"/>
-    <row r="602" ht="14.25" customHeight="1"/>
-    <row r="603" ht="14.25" customHeight="1"/>
-    <row r="604" ht="14.25" customHeight="1"/>
-    <row r="605" ht="14.25" customHeight="1"/>
-    <row r="606" ht="14.25" customHeight="1"/>
-    <row r="607" ht="14.25" customHeight="1"/>
-    <row r="608" ht="14.25" customHeight="1"/>
-    <row r="609" ht="14.25" customHeight="1"/>
-    <row r="610" ht="14.25" customHeight="1"/>
-    <row r="611" ht="14.25" customHeight="1"/>
-    <row r="612" ht="14.25" customHeight="1"/>
-    <row r="613" ht="14.25" customHeight="1"/>
-    <row r="614" ht="14.25" customHeight="1"/>
-    <row r="615" ht="14.25" customHeight="1"/>
-    <row r="616" ht="14.25" customHeight="1"/>
-    <row r="617" ht="14.25" customHeight="1"/>
-    <row r="618" ht="14.25" customHeight="1"/>
-    <row r="619" ht="14.25" customHeight="1"/>
-    <row r="620" ht="14.25" customHeight="1"/>
-    <row r="621" ht="14.25" customHeight="1"/>
-    <row r="622" ht="14.25" customHeight="1"/>
-    <row r="623" ht="14.25" customHeight="1"/>
-    <row r="624" ht="14.25" customHeight="1"/>
-    <row r="625" ht="14.25" customHeight="1"/>
-    <row r="626" ht="14.25" customHeight="1"/>
-    <row r="627" ht="14.25" customHeight="1"/>
-    <row r="628" ht="14.25" customHeight="1"/>
-    <row r="629" ht="14.25" customHeight="1"/>
-    <row r="630" ht="14.25" customHeight="1"/>
-    <row r="631" ht="14.25" customHeight="1"/>
-    <row r="632" ht="14.25" customHeight="1"/>
-    <row r="633" ht="14.25" customHeight="1"/>
-    <row r="634" ht="14.25" customHeight="1"/>
-    <row r="635" ht="14.25" customHeight="1"/>
-    <row r="636" ht="14.25" customHeight="1"/>
-    <row r="637" ht="14.25" customHeight="1"/>
-    <row r="638" ht="14.25" customHeight="1"/>
-    <row r="639" ht="14.25" customHeight="1"/>
-    <row r="640" ht="14.25" customHeight="1"/>
-    <row r="641" ht="14.25" customHeight="1"/>
-    <row r="642" ht="14.25" customHeight="1"/>
-    <row r="643" ht="14.25" customHeight="1"/>
-    <row r="644" ht="14.25" customHeight="1"/>
-    <row r="645" ht="14.25" customHeight="1"/>
-    <row r="646" ht="14.25" customHeight="1"/>
-    <row r="647" ht="14.25" customHeight="1"/>
-    <row r="648" ht="14.25" customHeight="1"/>
-    <row r="649" ht="14.25" customHeight="1"/>
-    <row r="650" ht="14.25" customHeight="1"/>
-    <row r="651" ht="14.25" customHeight="1"/>
-    <row r="652" ht="14.25" customHeight="1"/>
-    <row r="653" ht="14.25" customHeight="1"/>
-    <row r="654" ht="14.25" customHeight="1"/>
-    <row r="655" ht="14.25" customHeight="1"/>
-    <row r="656" ht="14.25" customHeight="1"/>
-    <row r="657" ht="14.25" customHeight="1"/>
-    <row r="658" ht="14.25" customHeight="1"/>
-    <row r="659" ht="14.25" customHeight="1"/>
-    <row r="660" ht="14.25" customHeight="1"/>
-    <row r="661" ht="14.25" customHeight="1"/>
-    <row r="662" ht="14.25" customHeight="1"/>
-    <row r="663" ht="14.25" customHeight="1"/>
-    <row r="664" ht="14.25" customHeight="1"/>
-    <row r="665" ht="14.25" customHeight="1"/>
-    <row r="666" ht="14.25" customHeight="1"/>
-    <row r="667" ht="14.25" customHeight="1"/>
-    <row r="668" ht="14.25" customHeight="1"/>
-    <row r="669" ht="14.25" customHeight="1"/>
-    <row r="670" ht="14.25" customHeight="1"/>
-    <row r="671" ht="14.25" customHeight="1"/>
-    <row r="672" ht="14.25" customHeight="1"/>
-    <row r="673" ht="14.25" customHeight="1"/>
-    <row r="674" ht="14.25" customHeight="1"/>
-    <row r="675" ht="14.25" customHeight="1"/>
-    <row r="676" ht="14.25" customHeight="1"/>
-    <row r="677" ht="14.25" customHeight="1"/>
-    <row r="678" ht="14.25" customHeight="1"/>
-    <row r="679" ht="14.25" customHeight="1"/>
-    <row r="680" ht="14.25" customHeight="1"/>
-    <row r="681" ht="14.25" customHeight="1"/>
-    <row r="682" ht="14.25" customHeight="1"/>
-    <row r="683" ht="14.25" customHeight="1"/>
-    <row r="684" ht="14.25" customHeight="1"/>
-    <row r="685" ht="14.25" customHeight="1"/>
-    <row r="686" ht="14.25" customHeight="1"/>
-    <row r="687" ht="14.25" customHeight="1"/>
-    <row r="688" ht="14.25" customHeight="1"/>
-    <row r="689" ht="14.25" customHeight="1"/>
-    <row r="690" ht="14.25" customHeight="1"/>
-    <row r="691" ht="14.25" customHeight="1"/>
-    <row r="692" ht="14.25" customHeight="1"/>
-    <row r="693" ht="14.25" customHeight="1"/>
-    <row r="694" ht="14.25" customHeight="1"/>
-    <row r="695" ht="14.25" customHeight="1"/>
-    <row r="696" ht="14.25" customHeight="1"/>
-    <row r="697" ht="14.25" customHeight="1"/>
-    <row r="698" ht="14.25" customHeight="1"/>
-    <row r="699" ht="14.25" customHeight="1"/>
-    <row r="700" ht="14.25" customHeight="1"/>
-    <row r="701" ht="14.25" customHeight="1"/>
-    <row r="702" ht="14.25" customHeight="1"/>
-    <row r="703" ht="14.25" customHeight="1"/>
-    <row r="704" ht="14.25" customHeight="1"/>
-    <row r="705" ht="14.25" customHeight="1"/>
-    <row r="706" ht="14.25" customHeight="1"/>
-    <row r="707" ht="14.25" customHeight="1"/>
-    <row r="708" ht="14.25" customHeight="1"/>
-    <row r="709" ht="14.25" customHeight="1"/>
-    <row r="710" ht="14.25" customHeight="1"/>
-    <row r="711" ht="14.25" customHeight="1"/>
-    <row r="712" ht="14.25" customHeight="1"/>
-    <row r="713" ht="14.25" customHeight="1"/>
-    <row r="714" ht="14.25" customHeight="1"/>
-    <row r="715" ht="14.25" customHeight="1"/>
-    <row r="716" ht="14.25" customHeight="1"/>
-    <row r="717" ht="14.25" customHeight="1"/>
-    <row r="718" ht="14.25" customHeight="1"/>
-    <row r="719" ht="14.25" customHeight="1"/>
-    <row r="720" ht="14.25" customHeight="1"/>
-    <row r="721" ht="14.25" customHeight="1"/>
-    <row r="722" ht="14.25" customHeight="1"/>
-    <row r="723" ht="14.25" customHeight="1"/>
-    <row r="724" ht="14.25" customHeight="1"/>
-    <row r="725" ht="14.25" customHeight="1"/>
-    <row r="726" ht="14.25" customHeight="1"/>
-    <row r="727" ht="14.25" customHeight="1"/>
-    <row r="728" ht="14.25" customHeight="1"/>
-    <row r="729" ht="14.25" customHeight="1"/>
-    <row r="730" ht="14.25" customHeight="1"/>
-    <row r="731" ht="14.25" customHeight="1"/>
-    <row r="732" ht="14.25" customHeight="1"/>
-    <row r="733" ht="14.25" customHeight="1"/>
-    <row r="734" ht="14.25" customHeight="1"/>
-    <row r="735" ht="14.25" customHeight="1"/>
-    <row r="736" ht="14.25" customHeight="1"/>
-    <row r="737" ht="14.25" customHeight="1"/>
-    <row r="738" ht="14.25" customHeight="1"/>
-    <row r="739" ht="14.25" customHeight="1"/>
-    <row r="740" ht="14.25" customHeight="1"/>
-    <row r="741" ht="14.25" customHeight="1"/>
-    <row r="742" ht="14.25" customHeight="1"/>
-    <row r="743" ht="14.25" customHeight="1"/>
-    <row r="744" ht="14.25" customHeight="1"/>
-    <row r="745" ht="14.25" customHeight="1"/>
-    <row r="746" ht="14.25" customHeight="1"/>
-    <row r="747" ht="14.25" customHeight="1"/>
-    <row r="748" ht="14.25" customHeight="1"/>
-    <row r="749" ht="14.25" customHeight="1"/>
-    <row r="750" ht="14.25" customHeight="1"/>
-    <row r="751" ht="14.25" customHeight="1"/>
-    <row r="752" ht="14.25" customHeight="1"/>
-    <row r="753" ht="14.25" customHeight="1"/>
-    <row r="754" ht="14.25" customHeight="1"/>
-    <row r="755" ht="14.25" customHeight="1"/>
-    <row r="756" ht="14.25" customHeight="1"/>
-    <row r="757" ht="14.25" customHeight="1"/>
-    <row r="758" ht="14.25" customHeight="1"/>
-    <row r="759" ht="14.25" customHeight="1"/>
-    <row r="760" ht="14.25" customHeight="1"/>
-    <row r="761" ht="14.25" customHeight="1"/>
-    <row r="762" ht="14.25" customHeight="1"/>
-    <row r="763" ht="14.25" customHeight="1"/>
-    <row r="764" ht="14.25" customHeight="1"/>
-    <row r="765" ht="14.25" customHeight="1"/>
-    <row r="766" ht="14.25" customHeight="1"/>
-    <row r="767" ht="14.25" customHeight="1"/>
-    <row r="768" ht="14.25" customHeight="1"/>
-    <row r="769" ht="14.25" customHeight="1"/>
-    <row r="770" ht="14.25" customHeight="1"/>
-    <row r="771" ht="14.25" customHeight="1"/>
-    <row r="772" ht="14.25" customHeight="1"/>
-    <row r="773" ht="14.25" customHeight="1"/>
-    <row r="774" ht="14.25" customHeight="1"/>
-    <row r="775" ht="14.25" customHeight="1"/>
-    <row r="776" ht="14.25" customHeight="1"/>
-    <row r="777" ht="14.25" customHeight="1"/>
-    <row r="778" ht="14.25" customHeight="1"/>
-    <row r="779" ht="14.25" customHeight="1"/>
-    <row r="780" ht="14.25" customHeight="1"/>
-    <row r="781" ht="14.25" customHeight="1"/>
-    <row r="782" ht="14.25" customHeight="1"/>
-    <row r="783" ht="14.25" customHeight="1"/>
-    <row r="784" ht="14.25" customHeight="1"/>
-    <row r="785" ht="14.25" customHeight="1"/>
-    <row r="786" ht="14.25" customHeight="1"/>
-    <row r="787" ht="14.25" customHeight="1"/>
-    <row r="788" ht="14.25" customHeight="1"/>
-    <row r="789" ht="14.25" customHeight="1"/>
-    <row r="790" ht="14.25" customHeight="1"/>
-    <row r="791" ht="14.25" customHeight="1"/>
-    <row r="792" ht="14.25" customHeight="1"/>
-    <row r="793" ht="14.25" customHeight="1"/>
-    <row r="794" ht="14.25" customHeight="1"/>
-    <row r="795" ht="14.25" customHeight="1"/>
-    <row r="796" ht="14.25" customHeight="1"/>
-    <row r="797" ht="14.25" customHeight="1"/>
-    <row r="798" ht="14.25" customHeight="1"/>
-    <row r="799" ht="14.25" customHeight="1"/>
-    <row r="800" ht="14.25" customHeight="1"/>
-    <row r="801" ht="14.25" customHeight="1"/>
-    <row r="802" ht="14.25" customHeight="1"/>
-    <row r="803" ht="14.25" customHeight="1"/>
-    <row r="804" ht="14.25" customHeight="1"/>
-    <row r="805" ht="14.25" customHeight="1"/>
-    <row r="806" ht="14.25" customHeight="1"/>
-    <row r="807" ht="14.25" customHeight="1"/>
-    <row r="808" ht="14.25" customHeight="1"/>
-    <row r="809" ht="14.25" customHeight="1"/>
-    <row r="810" ht="14.25" customHeight="1"/>
-    <row r="811" ht="14.25" customHeight="1"/>
-    <row r="812" ht="14.25" customHeight="1"/>
-    <row r="813" ht="14.25" customHeight="1"/>
-    <row r="814" ht="14.25" customHeight="1"/>
-    <row r="815" ht="14.25" customHeight="1"/>
-    <row r="816" ht="14.25" customHeight="1"/>
-    <row r="817" ht="14.25" customHeight="1"/>
-    <row r="818" ht="14.25" customHeight="1"/>
-    <row r="819" ht="14.25" customHeight="1"/>
-    <row r="820" ht="14.25" customHeight="1"/>
-    <row r="821" ht="14.25" customHeight="1"/>
-    <row r="822" ht="14.25" customHeight="1"/>
-    <row r="823" ht="14.25" customHeight="1"/>
-    <row r="824" ht="14.25" customHeight="1"/>
-    <row r="825" ht="14.25" customHeight="1"/>
-    <row r="826" ht="14.25" customHeight="1"/>
-    <row r="827" ht="14.25" customHeight="1"/>
-    <row r="828" ht="14.25" customHeight="1"/>
-    <row r="829" ht="14.25" customHeight="1"/>
-    <row r="830" ht="14.25" customHeight="1"/>
-    <row r="831" ht="14.25" customHeight="1"/>
-    <row r="832" ht="14.25" customHeight="1"/>
-    <row r="833" ht="14.25" customHeight="1"/>
-    <row r="834" ht="14.25" customHeight="1"/>
-    <row r="835" ht="14.25" customHeight="1"/>
-    <row r="836" ht="14.25" customHeight="1"/>
-    <row r="837" ht="14.25" customHeight="1"/>
-    <row r="838" ht="14.25" customHeight="1"/>
-    <row r="839" ht="14.25" customHeight="1"/>
-    <row r="840" ht="14.25" customHeight="1"/>
-    <row r="841" ht="14.25" customHeight="1"/>
-    <row r="842" ht="14.25" customHeight="1"/>
-    <row r="843" ht="14.25" customHeight="1"/>
-    <row r="844" ht="14.25" customHeight="1"/>
-    <row r="845" ht="14.25" customHeight="1"/>
-    <row r="846" ht="14.25" customHeight="1"/>
-    <row r="847" ht="14.25" customHeight="1"/>
-    <row r="848" ht="14.25" customHeight="1"/>
-    <row r="849" ht="14.25" customHeight="1"/>
-    <row r="850" ht="14.25" customHeight="1"/>
-    <row r="851" ht="14.25" customHeight="1"/>
-    <row r="852" ht="14.25" customHeight="1"/>
-    <row r="853" ht="14.25" customHeight="1"/>
-    <row r="854" ht="14.25" customHeight="1"/>
-    <row r="855" ht="14.25" customHeight="1"/>
-    <row r="856" ht="14.25" customHeight="1"/>
-    <row r="857" ht="14.25" customHeight="1"/>
-    <row r="858" ht="14.25" customHeight="1"/>
-    <row r="859" ht="14.25" customHeight="1"/>
-    <row r="860" ht="14.25" customHeight="1"/>
-    <row r="861" ht="14.25" customHeight="1"/>
-    <row r="862" ht="14.25" customHeight="1"/>
-    <row r="863" ht="14.25" customHeight="1"/>
-    <row r="864" ht="14.25" customHeight="1"/>
-    <row r="865" ht="14.25" customHeight="1"/>
-    <row r="866" ht="14.25" customHeight="1"/>
-    <row r="867" ht="14.25" customHeight="1"/>
-    <row r="868" ht="14.25" customHeight="1"/>
-    <row r="869" ht="14.25" customHeight="1"/>
-    <row r="870" ht="14.25" customHeight="1"/>
-    <row r="871" ht="14.25" customHeight="1"/>
-    <row r="872" ht="14.25" customHeight="1"/>
-    <row r="873" ht="14.25" customHeight="1"/>
-    <row r="874" ht="14.25" customHeight="1"/>
-    <row r="875" ht="14.25" customHeight="1"/>
-    <row r="876" ht="14.25" customHeight="1"/>
-    <row r="877" ht="14.25" customHeight="1"/>
-    <row r="878" ht="14.25" customHeight="1"/>
-    <row r="879" ht="14.25" customHeight="1"/>
-    <row r="880" ht="14.25" customHeight="1"/>
-    <row r="881" ht="14.25" customHeight="1"/>
-    <row r="882" ht="14.25" customHeight="1"/>
-    <row r="883" ht="14.25" customHeight="1"/>
-    <row r="884" ht="14.25" customHeight="1"/>
-    <row r="885" ht="14.25" customHeight="1"/>
-    <row r="886" ht="14.25" customHeight="1"/>
-    <row r="887" ht="14.25" customHeight="1"/>
-    <row r="888" ht="14.25" customHeight="1"/>
-    <row r="889" ht="14.25" customHeight="1"/>
-    <row r="890" ht="14.25" customHeight="1"/>
-    <row r="891" ht="14.25" customHeight="1"/>
-    <row r="892" ht="14.25" customHeight="1"/>
-    <row r="893" ht="14.25" customHeight="1"/>
-    <row r="894" ht="14.25" customHeight="1"/>
-    <row r="895" ht="14.25" customHeight="1"/>
-    <row r="896" ht="14.25" customHeight="1"/>
-    <row r="897" ht="14.25" customHeight="1"/>
-    <row r="898" ht="14.25" customHeight="1"/>
-    <row r="899" ht="14.25" customHeight="1"/>
-    <row r="900" ht="14.25" customHeight="1"/>
-    <row r="901" ht="14.25" customHeight="1"/>
-    <row r="902" ht="14.25" customHeight="1"/>
-    <row r="903" ht="14.25" customHeight="1"/>
-    <row r="904" ht="14.25" customHeight="1"/>
-    <row r="905" ht="14.25" customHeight="1"/>
-    <row r="906" ht="14.25" customHeight="1"/>
-    <row r="907" ht="14.25" customHeight="1"/>
-    <row r="908" ht="14.25" customHeight="1"/>
-    <row r="909" ht="14.25" customHeight="1"/>
-    <row r="910" ht="14.25" customHeight="1"/>
-    <row r="911" ht="14.25" customHeight="1"/>
-    <row r="912" ht="14.25" customHeight="1"/>
-    <row r="913" ht="14.25" customHeight="1"/>
-    <row r="914" ht="14.25" customHeight="1"/>
-    <row r="915" ht="14.25" customHeight="1"/>
-    <row r="916" ht="14.25" customHeight="1"/>
-    <row r="917" ht="14.25" customHeight="1"/>
-    <row r="918" ht="14.25" customHeight="1"/>
-    <row r="919" ht="14.25" customHeight="1"/>
-    <row r="920" ht="14.25" customHeight="1"/>
-    <row r="921" ht="14.25" customHeight="1"/>
-    <row r="922" ht="14.25" customHeight="1"/>
-    <row r="923" ht="14.25" customHeight="1"/>
-    <row r="924" ht="14.25" customHeight="1"/>
-    <row r="925" ht="14.25" customHeight="1"/>
-    <row r="926" ht="14.25" customHeight="1"/>
-    <row r="927" ht="14.25" customHeight="1"/>
-    <row r="928" ht="14.25" customHeight="1"/>
-    <row r="929" ht="14.25" customHeight="1"/>
-    <row r="930" ht="14.25" customHeight="1"/>
-    <row r="931" ht="14.25" customHeight="1"/>
-    <row r="932" ht="14.25" customHeight="1"/>
-    <row r="933" ht="14.25" customHeight="1"/>
-    <row r="934" ht="14.25" customHeight="1"/>
-    <row r="935" ht="14.25" customHeight="1"/>
-    <row r="936" ht="14.25" customHeight="1"/>
-    <row r="937" ht="14.25" customHeight="1"/>
-    <row r="938" ht="14.25" customHeight="1"/>
-    <row r="939" ht="14.25" customHeight="1"/>
-    <row r="940" ht="14.25" customHeight="1"/>
-    <row r="941" ht="14.25" customHeight="1"/>
-    <row r="942" ht="14.25" customHeight="1"/>
-    <row r="943" ht="14.25" customHeight="1"/>
-    <row r="944" ht="14.25" customHeight="1"/>
-    <row r="945" ht="14.25" customHeight="1"/>
-    <row r="946" ht="14.25" customHeight="1"/>
-    <row r="947" ht="14.25" customHeight="1"/>
-    <row r="948" ht="14.25" customHeight="1"/>
-    <row r="949" ht="14.25" customHeight="1"/>
-    <row r="950" ht="14.25" customHeight="1"/>
-    <row r="951" ht="14.25" customHeight="1"/>
-    <row r="952" ht="14.25" customHeight="1"/>
-    <row r="953" ht="14.25" customHeight="1"/>
-    <row r="954" ht="14.25" customHeight="1"/>
-    <row r="955" ht="14.25" customHeight="1"/>
-    <row r="956" ht="14.25" customHeight="1"/>
-    <row r="957" ht="14.25" customHeight="1"/>
-    <row r="958" ht="14.25" customHeight="1"/>
-    <row r="959" ht="14.25" customHeight="1"/>
-    <row r="960" ht="14.25" customHeight="1"/>
-    <row r="961" ht="14.25" customHeight="1"/>
-    <row r="962" ht="14.25" customHeight="1"/>
-    <row r="963" ht="14.25" customHeight="1"/>
-    <row r="964" ht="14.25" customHeight="1"/>
-    <row r="965" ht="14.25" customHeight="1"/>
-    <row r="966" ht="14.25" customHeight="1"/>
-    <row r="967" ht="14.25" customHeight="1"/>
-    <row r="968" ht="14.25" customHeight="1"/>
-    <row r="969" ht="14.25" customHeight="1"/>
-    <row r="970" ht="14.25" customHeight="1"/>
-    <row r="971" ht="14.25" customHeight="1"/>
-    <row r="972" ht="14.25" customHeight="1"/>
-    <row r="973" ht="14.25" customHeight="1"/>
-    <row r="974" ht="14.25" customHeight="1"/>
-    <row r="975" ht="14.25" customHeight="1"/>
-    <row r="976" ht="14.25" customHeight="1"/>
-    <row r="977" ht="14.25" customHeight="1"/>
-    <row r="978" ht="14.25" customHeight="1"/>
-    <row r="979" ht="14.25" customHeight="1"/>
-    <row r="980" ht="14.25" customHeight="1"/>
-    <row r="981" ht="14.25" customHeight="1"/>
-    <row r="982" ht="14.25" customHeight="1"/>
-    <row r="983" ht="14.25" customHeight="1"/>
-    <row r="984" ht="14.25" customHeight="1"/>
-    <row r="985" ht="14.25" customHeight="1"/>
-    <row r="986" ht="14.25" customHeight="1"/>
-    <row r="987" ht="14.25" customHeight="1"/>
-    <row r="988" ht="14.25" customHeight="1"/>
-    <row r="989" ht="14.25" customHeight="1"/>
-    <row r="990" ht="14.25" customHeight="1"/>
-    <row r="991" ht="14.25" customHeight="1"/>
-    <row r="992" ht="14.25" customHeight="1"/>
-    <row r="993" ht="14.25" customHeight="1"/>
-    <row r="994" ht="14.25" customHeight="1"/>
-    <row r="995" ht="14.25" customHeight="1"/>
-    <row r="996" ht="14.25" customHeight="1"/>
-    <row r="997" ht="14.25" customHeight="1"/>
-    <row r="998" ht="14.25" customHeight="1"/>
-    <row r="999" ht="14.25" customHeight="1"/>
-    <row r="1000" ht="14.25" customHeight="1"/>
+    <row r="152" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A152" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B152" s="1">
+        <v>1</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D152" s="3">
+        <v>102</v>
+      </c>
+      <c r="E152" s="3">
+        <v>0</v>
+      </c>
+      <c r="F152" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A153" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B153" s="1">
+        <v>2</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D153" s="3">
+        <v>38</v>
+      </c>
+      <c r="E153" s="3">
+        <v>0</v>
+      </c>
+      <c r="F153" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A154" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B154" s="1">
+        <v>3</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D154" s="3">
+        <v>37</v>
+      </c>
+      <c r="E154" s="3">
+        <v>0</v>
+      </c>
+      <c r="F154" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A155" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B155" s="1">
+        <v>4</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D155" s="3">
+        <v>45</v>
+      </c>
+      <c r="E155" s="3">
+        <v>0</v>
+      </c>
+      <c r="F155" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A156" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B156" s="1">
+        <v>5</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D156" s="3">
+        <v>35</v>
+      </c>
+      <c r="E156" s="3">
+        <v>0</v>
+      </c>
+      <c r="F156" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A157" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B157" s="1">
+        <v>6</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D157" s="3">
+        <v>48</v>
+      </c>
+      <c r="E157" s="3">
+        <v>0</v>
+      </c>
+      <c r="F157" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A158" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B158" s="1">
+        <v>7</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D158" s="3">
+        <v>30</v>
+      </c>
+      <c r="E158" s="3">
+        <v>0</v>
+      </c>
+      <c r="F158" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A159" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B159" s="1">
+        <v>8</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D159" s="3">
+        <v>23</v>
+      </c>
+      <c r="E159" s="3">
+        <v>0</v>
+      </c>
+      <c r="F159" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A160" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B160" s="1">
+        <v>9</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D160" s="3">
+        <v>40</v>
+      </c>
+      <c r="E160" s="3">
+        <v>0</v>
+      </c>
+      <c r="F160" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A161" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B161" s="1">
+        <v>10</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D161" s="3">
+        <v>49</v>
+      </c>
+      <c r="E161" s="3">
+        <v>0</v>
+      </c>
+      <c r="F161" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C162" s="1"/>
+    </row>
+    <row r="163" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C163" s="1"/>
+    </row>
+    <row r="164" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="165" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="166" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="167" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="168" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="169" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="170" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="171" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="172" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="173" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="174" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="175" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="176" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="177" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="178" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="179" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="180" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="181" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="182" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="183" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="184" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="185" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="186" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="187" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="188" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="189" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="190" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="191" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="192" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="193" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="194" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="195" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="196" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="197" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="198" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="199" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="200" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="201" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="202" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="203" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="204" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="205" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="206" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="207" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="208" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="209" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="210" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="211" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="212" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="213" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="214" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="215" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="216" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="217" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="218" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="219" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="220" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="221" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="222" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="223" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="224" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="225" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="226" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="227" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="228" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="229" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="230" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="231" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="232" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="233" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="234" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="235" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="236" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="237" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="238" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="239" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="240" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="241" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="242" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="243" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="244" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="245" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="246" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="247" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="248" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="249" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="250" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="251" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="252" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="253" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="254" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="255" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="256" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="257" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="258" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="259" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="260" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="261" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="262" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="263" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="264" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="265" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="266" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="267" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="268" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="269" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="270" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="271" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="272" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="273" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="274" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="275" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="276" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="277" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="278" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="279" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="280" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="281" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="282" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="283" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="284" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="285" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="286" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="287" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="288" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="289" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="290" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="291" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="292" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="293" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="294" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="295" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="296" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="297" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="298" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="299" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="300" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="301" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="302" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="303" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="304" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="305" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="306" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="307" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="308" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="309" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="310" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="311" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="312" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="313" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="314" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="315" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="316" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="317" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="318" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="319" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="320" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="321" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="322" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="323" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="324" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="325" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="326" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="327" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="328" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="329" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="330" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="331" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="332" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="333" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="334" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="335" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="336" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="337" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="338" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="339" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="340" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="341" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="342" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="343" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="344" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="345" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="346" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="347" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="348" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="349" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="350" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="351" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="352" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="353" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="354" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="355" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="356" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="357" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="358" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="359" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="360" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="361" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="362" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="363" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="364" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="365" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="366" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="367" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="368" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="369" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="370" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="371" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="372" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="373" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="374" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="375" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="376" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="377" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="378" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="379" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="380" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="381" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="382" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="383" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="384" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="385" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="386" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="387" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="388" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="389" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="390" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="391" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="392" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="393" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="394" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="395" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="396" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="397" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="398" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="399" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="400" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="401" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="402" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="403" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="404" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="405" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="406" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="407" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="408" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="409" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="410" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="411" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="412" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="413" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="414" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="415" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="416" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="417" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="418" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="419" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="420" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="421" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="422" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="423" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="424" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="425" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="426" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="427" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="428" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="429" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="430" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="431" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="432" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="433" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="434" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="435" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="436" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="437" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="438" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="439" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="440" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="441" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="442" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="443" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="444" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="445" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="446" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="447" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="448" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="449" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="450" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="451" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="452" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="453" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="454" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="455" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="456" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="457" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="458" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="459" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="460" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="461" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="462" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="463" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="464" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="465" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="466" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="467" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="468" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="469" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="470" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="471" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="472" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="473" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="474" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="475" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="476" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="477" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="478" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="479" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="480" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="481" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="482" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="483" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="484" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="485" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="486" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="487" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="488" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="489" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="490" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="491" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="492" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="493" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="494" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="495" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="496" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="497" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="498" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="499" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="500" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="501" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="502" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="503" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="504" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="505" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="506" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="507" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="508" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="509" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="510" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="511" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="512" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="513" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="514" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="515" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="516" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="517" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="518" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="519" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="520" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="521" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="522" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="523" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="524" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="525" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="526" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="527" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="528" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="529" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="530" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="531" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="532" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="533" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="534" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="535" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="536" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="537" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="538" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="539" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="540" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="541" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="542" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="543" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="544" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="545" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="546" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="547" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="548" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="549" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="550" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="551" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="552" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="553" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="554" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="555" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="556" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="557" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="558" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="559" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="560" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="561" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="562" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="563" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="564" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="565" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="566" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="567" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="568" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="569" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="570" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="571" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="572" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="573" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="574" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="575" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="576" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="577" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="578" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="579" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="580" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="581" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="582" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="583" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="584" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="585" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="586" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="587" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="588" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="589" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="590" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="591" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="592" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="593" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="594" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="595" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="596" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="597" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="598" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="599" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="600" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="601" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="602" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="603" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="604" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="605" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="606" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="607" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="608" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="609" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="610" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="611" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="612" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="613" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="614" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="615" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="616" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="617" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="618" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="619" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="620" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="621" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="622" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="623" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="624" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="625" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="626" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="627" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="628" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="629" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="630" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="631" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="632" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="633" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="634" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="635" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="636" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="637" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="638" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="639" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="640" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="641" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="642" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="643" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="644" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="645" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="646" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="647" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="648" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="649" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="650" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="651" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="652" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="653" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="654" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="655" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="656" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="657" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="658" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="659" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="660" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="661" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="662" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="663" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="664" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="665" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="666" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="667" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="668" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="669" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="670" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="671" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="672" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="673" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="674" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="675" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="676" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="677" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="678" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="679" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="680" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="681" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="682" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="683" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="684" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="685" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="686" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="687" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="688" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="689" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="690" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="691" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="692" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="693" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="694" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="695" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="696" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="697" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="698" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="699" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="700" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="701" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="702" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="703" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="704" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="705" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="706" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="707" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="708" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="709" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="710" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="711" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="712" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="713" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="714" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="715" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="716" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="717" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="718" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="719" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="720" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="721" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="722" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="723" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="724" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="725" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="726" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="727" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="728" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="729" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="730" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="731" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="732" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="733" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="734" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="735" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="736" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="737" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="738" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="739" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="740" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="741" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="742" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="743" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="744" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="745" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="746" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="747" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="748" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="749" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="750" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="751" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="752" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="753" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="754" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="755" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="756" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="757" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="758" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="759" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="760" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="761" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="762" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="763" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="764" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="765" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="766" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="767" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="768" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="769" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="770" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="771" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="772" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="773" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="774" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="775" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="776" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="777" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="778" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="779" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="780" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="781" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="782" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="783" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="784" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="785" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="786" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="787" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="788" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="789" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="790" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="791" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="792" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="793" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="794" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="795" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="796" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="797" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="798" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="799" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="800" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="801" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="802" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="803" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="804" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="805" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="806" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="807" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="808" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="809" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="810" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="811" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="812" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="813" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="814" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="815" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="816" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="817" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="818" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="819" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="820" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="821" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="822" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="823" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="824" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="825" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="826" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="827" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="828" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="829" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="830" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="831" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="832" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="833" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="834" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="835" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="836" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="837" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="838" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="839" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="840" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="841" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="842" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="843" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="844" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="845" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="846" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="847" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="848" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="849" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="850" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="851" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="852" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="853" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="854" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="855" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="856" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="857" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="858" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="859" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="860" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="861" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="862" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="863" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="864" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="865" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="866" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="867" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="868" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="869" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="870" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="871" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="872" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="873" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="874" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="875" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="876" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="877" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="878" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="879" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="880" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="881" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="882" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="883" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="884" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="885" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="886" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="887" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="888" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="889" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="890" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="891" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="892" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="893" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="894" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="895" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="896" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="897" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="898" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="899" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="900" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="901" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="902" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="903" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="904" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="905" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="906" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="907" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="908" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="909" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="910" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="911" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="912" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="913" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="914" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="915" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="916" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="917" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="918" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="919" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="920" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="921" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="922" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="923" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="924" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="925" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="926" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="927" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="928" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="929" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="930" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="931" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="932" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="933" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="934" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="935" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="936" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="937" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="938" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="939" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="940" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="941" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="942" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="943" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="944" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="945" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="946" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="947" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="948" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="949" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="950" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="951" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="952" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="953" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="954" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="955" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="956" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="957" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="958" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="959" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="960" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="961" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="962" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="963" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="964" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="965" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="966" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="967" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="968" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="969" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="970" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="971" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="972" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="973" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="974" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="975" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="976" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="977" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="978" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="979" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="980" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="981" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="982" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="983" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="984" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="985" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="986" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="987" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="988" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="989" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="990" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="991" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="992" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="993" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="994" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="995" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="996" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="997" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="998" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="999" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>